--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>23/04/2025</t>
+    <t>05/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -50,7 +50,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Auxiliar de Supervision</t>
+    <t>Supervisor Operaciones</t>
   </si>
   <si>
     <t>Región:</t>
@@ -86,238 +86,232 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>FNY9FG3</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Doking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>POLY</t>
+  </si>
+  <si>
+    <t>VVX 250</t>
+  </si>
+  <si>
+    <t>482567106BD7</t>
+  </si>
+  <si>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP Compaq Pro 6300</t>
+  </si>
+  <si>
+    <t>MXL31500FJ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00078</t>
+  </si>
+  <si>
+    <t>Acteck</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>20-07-10112</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>JB6P283</t>
+  </si>
+  <si>
+    <t>KB3322Wt</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WW-A00</t>
+  </si>
+  <si>
+    <t>WM118t</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WW-A00</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FWT</t>
+  </si>
+  <si>
+    <t>BENQ</t>
+  </si>
+  <si>
+    <t>GW2780-T</t>
+  </si>
+  <si>
+    <t>ETK1N0041701Q</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WV-A00</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WV-A00</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>VVX 150</t>
+  </si>
+  <si>
+    <t>64167F7F514D</t>
+  </si>
+  <si>
+    <t>24-07-57974</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>JSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00086</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-00CU</t>
+  </si>
+  <si>
+    <t>827P283</t>
+  </si>
+  <si>
+    <t>ActeCK</t>
+  </si>
+  <si>
+    <t>22-04-05212</t>
+  </si>
+  <si>
+    <t>4TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00076</t>
+  </si>
+  <si>
+    <t>Cargador Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
     <t>Pantalla TV</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>UN50J5200AFXZX</t>
-  </si>
-  <si>
-    <t>061W3CNJ801661W</t>
-  </si>
-  <si>
-    <t>xcuyilkgjhohjlkvn</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>7BV9FG3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00050</t>
-  </si>
-  <si>
-    <t>Cargador Laptop</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>3W9J0C3</t>
-  </si>
-  <si>
-    <t>Cargador de Doking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>ACTECK</t>
-  </si>
-  <si>
-    <t>MK450</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>6W69G04</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216R</t>
-  </si>
-  <si>
-    <t>23-08-29697</t>
-  </si>
-  <si>
-    <t>Mochila</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>POLY</t>
-  </si>
-  <si>
-    <t>VVX 250</t>
-  </si>
-  <si>
-    <t>482567106BD7</t>
-  </si>
-  <si>
-    <t>Desktop/Monitor</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>HP Compaq Pro 6300</t>
-  </si>
-  <si>
-    <t>MXL31500FJ</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00078</t>
-  </si>
-  <si>
-    <t>Acteck</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>20-07-10112</t>
-  </si>
-  <si>
-    <t>E2720HS</t>
-  </si>
-  <si>
-    <t>JB6P283</t>
-  </si>
-  <si>
-    <t>KB3322Wt</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-K6WW-A00</t>
-  </si>
-  <si>
-    <t>WM118t</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-M6WW-A00</t>
-  </si>
-  <si>
-    <t>EliteDisplay E231</t>
-  </si>
-  <si>
-    <t>6CM4083FWT</t>
-  </si>
-  <si>
-    <t>BENQ</t>
-  </si>
-  <si>
-    <t>GW2780-T</t>
-  </si>
-  <si>
-    <t>ETK1N0041701Q</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-M6WV-A00</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-K6WV-A00</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>64167F7F514D</t>
-  </si>
-  <si>
-    <t>24-07-57974</t>
-  </si>
-  <si>
-    <t>Optiplex 7490 AIO</t>
-  </si>
-  <si>
-    <t>JSYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00086</t>
-  </si>
-  <si>
-    <t>KB216T</t>
-  </si>
-  <si>
-    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
-  </si>
-  <si>
-    <t>MS116T1</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-00CU</t>
-  </si>
-  <si>
-    <t>827P283</t>
-  </si>
-  <si>
-    <t>ActeCK</t>
-  </si>
-  <si>
-    <t>22-04-05212</t>
-  </si>
-  <si>
-    <t>4TYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00076</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Optiplex 3050</t>
-  </si>
-  <si>
-    <t>9NK8CM2</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00079</t>
   </si>
   <si>
     <t>LG</t>
@@ -1210,17 +1204,17 @@
         <v>2</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="38"/>
       <c r="H20" s="38"/>
@@ -1231,7 +1225,7 @@
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -1244,59 +1238,51 @@
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="38">
-        <v>4</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1304,20 +1290,20 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E25" s="38"/>
-      <c r="F25" s="38">
-        <v>368631741364</v>
+      <c r="F25" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1325,16 +1311,16 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38">
@@ -1346,20 +1332,20 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="38">
-        <v>1929</v>
+        <v>40</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>41</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38">
-        <v>730320922522</v>
+        <v>368631741364</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1367,20 +1353,20 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="D28" s="38">
+        <v>1929</v>
       </c>
       <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
-        <v>48</v>
+      <c r="F28" s="38">
+        <v>730320922522</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1388,20 +1374,20 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1409,20 +1395,20 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1430,20 +1416,20 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1451,71 +1437,71 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="A33" s="38">
+        <v>13</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="38">
-        <v>14</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38">
-        <v>368631740944</v>
-      </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -1527,20 +1513,20 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>66</v>
+      <c r="F36" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1548,60 +1534,60 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
+      <c r="F37" s="38" t="s">
+        <v>64</v>
+      </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E38" s="38"/>
-      <c r="F38" s="38" t="s">
-        <v>68</v>
-      </c>
+      <c r="F38" s="38"/>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1609,20 +1595,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1630,20 +1616,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1651,20 +1637,20 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1672,20 +1658,20 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1693,20 +1679,20 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>69</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1714,20 +1700,20 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1735,20 +1721,20 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1756,75 +1742,75 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
+      <c r="A48" s="38">
+        <v>27</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="38">
-        <v>28</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -1832,20 +1818,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -1853,56 +1839,56 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D52" s="38" t="s">
         <v>65</v>
       </c>
       <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
+      <c r="F52" s="38" t="s">
+        <v>89</v>
+      </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E53" s="38"/>
-      <c r="F53" s="38">
-        <v>368631741367</v>
-      </c>
+      <c r="F53" s="38"/>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="38" t="s">
         <v>41</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>43</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38">
@@ -1914,20 +1900,20 @@
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38" t="s">
-        <v>93</v>
+      <c r="F55" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1935,88 +1921,96 @@
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22" t="s">
+      <c r="A57" s="38">
+        <v>35</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+    </row>
+    <row r="58" spans="1:10" customHeight="1" ht="15">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+    </row>
+    <row r="59" spans="1:10" customHeight="1" ht="15">
+      <c r="A59" s="38">
+        <v>36</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-    </row>
-    <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="38">
-        <v>36</v>
-      </c>
-      <c r="B58" s="38" t="s">
+      <c r="E59" s="38"/>
+      <c r="F59" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-    </row>
-    <row r="59" spans="1:10" customHeight="1" ht="15">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
         <v>37</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
@@ -2027,17 +2021,17 @@
         <v>38</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -2048,7 +2042,7 @@
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
       <c r="D62" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -2080,7 +2074,7 @@
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
       <c r="A65" s="26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="26"/>
@@ -2104,7 +2098,7 @@
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -2117,7 +2111,7 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B68" s="28"/>
       <c r="C68" s="28"/>
@@ -2130,7 +2124,7 @@
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
       <c r="A69" s="28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B69" s="28"/>
       <c r="C69" s="28"/>
@@ -2143,7 +2137,7 @@
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="24.05">
       <c r="A70" s="29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -2157,7 +2151,7 @@
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="27">
       <c r="A71" s="28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B71" s="28"/>
       <c r="C71" s="28"/>
@@ -2181,7 +2175,7 @@
     </row>
     <row r="73" spans="1:10" customHeight="1" ht="39">
       <c r="A73" s="31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
@@ -2217,14 +2211,14 @@
     <row r="76" spans="1:10" customHeight="1" ht="15">
       <c r="A76" s="32"/>
       <c r="B76" s="34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C76" s="34"/>
       <c r="D76" s="34"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H76" s="35"/>
       <c r="I76" s="35"/>
@@ -2234,7 +2228,7 @@
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="36" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
@@ -2267,7 +2261,7 @@
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="2"/>
       <c r="B80" s="34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C80" s="34"/>
       <c r="D80" s="34"/>
@@ -2283,7 +2277,7 @@
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
       <c r="B81" s="34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C81" s="34"/>
       <c r="D81" s="34"/>
@@ -2291,7 +2285,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="34" t="str">
         <f>C12</f>
-        <v>Auxiliar de Supervision</v>
+        <v>Supervisor Operaciones</v>
       </c>
       <c r="H81" s="34"/>
       <c r="I81" s="34"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="111">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>05/05/2025</t>
+    <t>08/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -50,7 +50,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Supervisor Operaciones</t>
+    <t>Coordinador de Información Financiera</t>
   </si>
   <si>
     <t>Región:</t>
@@ -95,12 +95,6 @@
     <t>Latitude 5520</t>
   </si>
   <si>
-    <t>FNY9FG3</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
     <t>7BV9FG3</t>
   </si>
   <si>
@@ -128,7 +122,7 @@
     <t>3W9J0C3</t>
   </si>
   <si>
-    <t>Cargador de Doking</t>
+    <t>Cargador de Docking</t>
   </si>
   <si>
     <t>HA180MP180</t>
@@ -182,7 +176,7 @@
     <t>Telefono</t>
   </si>
   <si>
-    <t>POLY</t>
+    <t>Poly</t>
   </si>
   <si>
     <t>VVX 250</t>
@@ -206,9 +200,6 @@
     <t>DVZ-VH-TI-00078</t>
   </si>
   <si>
-    <t>Acteck</t>
-  </si>
-  <si>
     <t>5216 R</t>
   </si>
   <si>
@@ -290,9 +281,6 @@
     <t>827P283</t>
   </si>
   <si>
-    <t>ActeCK</t>
-  </si>
-  <si>
     <t>22-04-05212</t>
   </si>
   <si>
@@ -302,7 +290,7 @@
     <t>DVZ-VH-TI-00076</t>
   </si>
   <si>
-    <t>Cargador Laptop</t>
+    <t>Cargador de Laptop</t>
   </si>
   <si>
     <t>LA65NM190</t>
@@ -314,7 +302,7 @@
     <t>Pantalla TV</t>
   </si>
   <si>
-    <t>LG</t>
+    <t>Lg</t>
   </si>
   <si>
     <t>43UQ8008PSB</t>
@@ -359,10 +347,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Supervisor TI</t>
+    <t>Abraham Palayot Sanchez</t>
+  </si>
+  <si>
+    <t>Informacion Financiera</t>
   </si>
 </sst>
 </file>
@@ -1194,95 +1182,93 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="1:10" customHeight="1" ht="15">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="38"/>
-    </row>
-    <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="B21" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" customHeight="1" ht="15">
+      <c r="A23" s="38">
         <v>3</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="38" t="s">
+      <c r="B23" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-    </row>
-    <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
         <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1293,17 +1279,17 @@
         <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="38"/>
-      <c r="F25" s="38" t="s">
-        <v>38</v>
+      <c r="F25" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1314,13 +1300,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>41</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38">
@@ -1335,17 +1321,17 @@
         <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="38" t="s">
         <v>41</v>
+      </c>
+      <c r="D27" s="38">
+        <v>1929</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38">
-        <v>368631741364</v>
+        <v>730320922522</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1359,14 +1345,14 @@
         <v>42</v>
       </c>
       <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="38">
-        <v>1929</v>
-      </c>
       <c r="E28" s="38"/>
-      <c r="F28" s="38">
-        <v>730320922522</v>
+      <c r="F28" s="38" t="s">
+        <v>44</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1377,17 +1363,17 @@
         <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1398,13 +1384,13 @@
         <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
@@ -1425,11 +1411,11 @@
         <v>52</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1440,68 +1426,68 @@
         <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="38">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="38">
         <v>13</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="B34" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38">
+        <v>368631740944</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
         <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>41</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -1516,17 +1502,17 @@
         <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>368631740944</v>
+      <c r="F36" s="38" t="s">
+        <v>61</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1537,17 +1523,17 @@
         <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="38" t="s">
         <v>47</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>63</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1558,16 +1544,18 @@
         <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
+      <c r="F38" s="38" t="s">
+        <v>63</v>
+      </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
@@ -1577,17 +1565,17 @@
         <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1598,17 +1586,17 @@
         <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1622,14 +1610,14 @@
         <v>42</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1640,10 +1628,10 @@
         <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>71</v>
@@ -1661,17 +1649,17 @@
         <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1682,17 +1670,17 @@
         <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C44" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1703,13 +1691,13 @@
         <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
@@ -1724,17 +1712,17 @@
         <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1745,72 +1733,72 @@
         <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="38">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="38">
         <v>27</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="38" t="s">
+      <c r="B49" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D49" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38" t="s">
+      <c r="E49" s="38"/>
+      <c r="F49" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
         <v>28</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C50" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -1827,11 +1815,11 @@
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -1842,17 +1830,17 @@
         <v>30</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -1863,16 +1851,18 @@
         <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
+      <c r="F53" s="38">
+        <v>368631741367</v>
+      </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
@@ -1882,13 +1872,13 @@
         <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38">
@@ -1903,17 +1893,17 @@
         <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38">
-        <v>368631741367</v>
+      <c r="F55" s="38" t="s">
+        <v>87</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1924,65 +1914,65 @@
         <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="38">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+    </row>
+    <row r="58" spans="1:10" customHeight="1" ht="15">
+      <c r="A58" s="38">
         <v>35</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="38" t="s">
+      <c r="B58" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38" t="s">
+      <c r="D58" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-    </row>
-    <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
         <v>36</v>
       </c>
       <c r="B59" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="38" t="s">
         <v>94</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D59" s="38" t="s">
         <v>95</v>
@@ -2000,105 +1990,97 @@
         <v>37</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="38">
-        <v>38</v>
-      </c>
-      <c r="B61" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D61" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
+      <c r="A64" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="27"/>
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="27"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
+      <c r="A66" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -2111,7 +2093,7 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B68" s="28"/>
       <c r="C68" s="28"/>
@@ -2122,173 +2104,171 @@
       <c r="H68" s="28"/>
       <c r="I68" s="28"/>
     </row>
-    <row r="69" spans="1:10" customHeight="1" ht="15">
-      <c r="A69" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A70" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" customHeight="1" ht="27">
-      <c r="A71" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-    </row>
-    <row r="72" spans="1:10" customHeight="1" ht="15">
-      <c r="A72" s="30"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="39">
-      <c r="A73" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
+    <row r="69" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A69" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="27">
+      <c r="A70" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+    </row>
+    <row r="71" spans="1:10" customHeight="1" ht="15">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+    </row>
+    <row r="72" spans="1:10" customHeight="1" ht="39">
+      <c r="A72" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="15">
+      <c r="A73" s="32"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="33"/>
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="32"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="32"/>
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="33"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="33"/>
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="2"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
+      <c r="A75" s="32"/>
+      <c r="B75" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
+      <c r="G75" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="32"/>
-      <c r="B76" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="36" t="s">
+        <v>108</v>
+      </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="36" t="s">
-        <v>112</v>
-      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="2"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="B79" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="G79" s="34" t="str">
+        <f>C10</f>
+        <v>Cristell Hernandez Contreras</v>
+      </c>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="2"/>
       <c r="B80" s="34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C80" s="34"/>
       <c r="D80" s="34"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="34" t="str">
-        <f>C10</f>
-        <v>Cristell Hernandez Contreras</v>
+        <f>C12</f>
+        <v>Coordinador de Información Financiera</v>
       </c>
       <c r="H80" s="34"/>
       <c r="I80" s="34"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
-      <c r="B81" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="34" t="str">
-        <f>C12</f>
-        <v>Supervisor Operaciones</v>
-      </c>
-      <c r="H81" s="34"/>
-      <c r="I81" s="34"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="2"/>
@@ -2297,31 +2277,20 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:10" customHeight="1" ht="15">
-      <c r="A84" s="32"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2340,23 +2309,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="G79:I79"/>
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="G80:I80"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="G81:I81"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2486,10 +2455,7 @@
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="H61:I61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H19:I62"/>
+    <mergeCell ref="H19:I61"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="114">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>23/04/2025</t>
+    <t>09/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,238 +86,229 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>Se entrego equipo</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Doking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>POLY</t>
+  </si>
+  <si>
+    <t>VVX 250</t>
+  </si>
+  <si>
+    <t>482567106BD7</t>
+  </si>
+  <si>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP Compaq Pro 6300</t>
+  </si>
+  <si>
+    <t>MXL31500FJ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00078</t>
+  </si>
+  <si>
+    <t>Acteck</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>20-07-10112</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>JB6P283</t>
+  </si>
+  <si>
+    <t>KB3322Wt</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WW-A00</t>
+  </si>
+  <si>
+    <t>WM118t</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WW-A00</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FWT</t>
+  </si>
+  <si>
+    <t>BENQ</t>
+  </si>
+  <si>
+    <t>GW2780-T</t>
+  </si>
+  <si>
+    <t>ETK1N0041701Q</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WV-A00</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WV-A00</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>VVX 150</t>
+  </si>
+  <si>
+    <t>64167F7F514D</t>
+  </si>
+  <si>
+    <t>24-07-57974</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>JSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00086</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-00CU</t>
+  </si>
+  <si>
+    <t>827P283</t>
+  </si>
+  <si>
+    <t>ActeCK</t>
+  </si>
+  <si>
+    <t>22-04-05212</t>
+  </si>
+  <si>
+    <t>4TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00076</t>
+  </si>
+  <si>
+    <t>Cargador Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
     <t>Pantalla TV</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>UN50J5200AFXZX</t>
-  </si>
-  <si>
-    <t>061W3CNJ801661W</t>
-  </si>
-  <si>
-    <t>xcuyilkgjhohjlkvn</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>7BV9FG3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00050</t>
-  </si>
-  <si>
-    <t>Cargador Laptop</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>3W9J0C3</t>
-  </si>
-  <si>
-    <t>Cargador de Doking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>ACTECK</t>
-  </si>
-  <si>
-    <t>MK450</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>6W69G04</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216R</t>
-  </si>
-  <si>
-    <t>23-08-29697</t>
-  </si>
-  <si>
-    <t>Mochila</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>POLY</t>
-  </si>
-  <si>
-    <t>VVX 250</t>
-  </si>
-  <si>
-    <t>482567106BD7</t>
-  </si>
-  <si>
-    <t>Desktop/Monitor</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>HP Compaq Pro 6300</t>
-  </si>
-  <si>
-    <t>MXL31500FJ</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00078</t>
-  </si>
-  <si>
-    <t>Acteck</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>20-07-10112</t>
-  </si>
-  <si>
-    <t>E2720HS</t>
-  </si>
-  <si>
-    <t>JB6P283</t>
-  </si>
-  <si>
-    <t>KB3322Wt</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-K6WW-A00</t>
-  </si>
-  <si>
-    <t>WM118t</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-M6WW-A00</t>
-  </si>
-  <si>
-    <t>EliteDisplay E231</t>
-  </si>
-  <si>
-    <t>6CM4083FWT</t>
-  </si>
-  <si>
-    <t>BENQ</t>
-  </si>
-  <si>
-    <t>GW2780-T</t>
-  </si>
-  <si>
-    <t>ETK1N0041701Q</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-M6WV-A00</t>
-  </si>
-  <si>
-    <t>CN-0255KM-LO300-217-K6WV-A00</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>64167F7F514D</t>
-  </si>
-  <si>
-    <t>24-07-57974</t>
-  </si>
-  <si>
-    <t>Optiplex 7490 AIO</t>
-  </si>
-  <si>
-    <t>JSYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00086</t>
-  </si>
-  <si>
-    <t>KB216T</t>
-  </si>
-  <si>
-    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
-  </si>
-  <si>
-    <t>MS116T1</t>
-  </si>
-  <si>
-    <t>CN-065K5F-LO300-150-00CU</t>
-  </si>
-  <si>
-    <t>827P283</t>
-  </si>
-  <si>
-    <t>ActeCK</t>
-  </si>
-  <si>
-    <t>22-04-05212</t>
-  </si>
-  <si>
-    <t>4TYKTH3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00076</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Optiplex 3050</t>
-  </si>
-  <si>
-    <t>9NK8CM2</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00079</t>
   </si>
   <si>
     <t>LG</t>
@@ -1206,76 +1197,68 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="B21" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="C21" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22" t="s">
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:10" customHeight="1" ht="15">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-    </row>
-    <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
-        <v>3</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1283,20 +1266,20 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1304,16 +1287,16 @@
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38">
@@ -1325,16 +1308,16 @@
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
       <c r="A26" s="38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38">
@@ -1346,13 +1329,13 @@
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D27" s="38">
         <v>1929</v>
@@ -1367,20 +1350,20 @@
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
       <c r="A28" s="38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1388,20 +1371,20 @@
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1409,20 +1392,20 @@
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1430,20 +1413,20 @@
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1451,20 +1434,20 @@
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1475,7 +1458,7 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -1485,16 +1468,16 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38">
@@ -1506,16 +1489,16 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -1527,20 +1510,20 @@
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1548,16 +1531,16 @@
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38"/>
@@ -1567,20 +1550,20 @@
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1588,20 +1571,20 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1609,20 +1592,20 @@
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1630,20 +1613,20 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1651,20 +1634,20 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="38">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1672,20 +1655,20 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
+        <v>22</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>28</v>
-      </c>
       <c r="D43" s="38" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1693,20 +1676,20 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1714,20 +1697,20 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1735,20 +1718,20 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1756,20 +1739,20 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -1780,7 +1763,7 @@
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
       <c r="D48" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -1790,20 +1773,20 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
@@ -1811,20 +1794,20 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -1832,20 +1815,20 @@
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -1853,16 +1836,16 @@
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="38">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38"/>
@@ -1872,16 +1855,16 @@
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38">
@@ -1893,16 +1876,16 @@
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="38">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38">
@@ -1914,20 +1897,20 @@
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1935,20 +1918,20 @@
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
       <c r="A56" s="38">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -1959,7 +1942,7 @@
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
       <c r="D57" s="22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -1969,142 +1952,142 @@
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
       <c r="A58" s="38">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22" t="s">
+      <c r="A59" s="38">
+        <v>36</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
         <v>37</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="38">
-        <v>38</v>
-      </c>
-      <c r="B61" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+    </row>
+    <row r="62" spans="1:10" customHeight="1" ht="15">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+    </row>
+    <row r="63" spans="1:10" customHeight="1" ht="15">
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+    </row>
+    <row r="64" spans="1:10" customHeight="1" ht="15">
+      <c r="A64" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+    </row>
+    <row r="65" spans="1:10" customHeight="1" ht="15">
+      <c r="A65" s="27"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="27"/>
+    </row>
+    <row r="66" spans="1:10" customHeight="1" ht="15">
+      <c r="A66" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-    </row>
-    <row r="62" spans="1:10" customHeight="1" ht="15">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-    </row>
-    <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
-    </row>
-    <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-    </row>
-    <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-    </row>
-    <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="27"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -2117,7 +2100,7 @@
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
       <c r="A68" s="28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B68" s="28"/>
       <c r="C68" s="28"/>
@@ -2128,173 +2111,171 @@
       <c r="H68" s="28"/>
       <c r="I68" s="28"/>
     </row>
-    <row r="69" spans="1:10" customHeight="1" ht="15">
-      <c r="A69" s="28" t="s">
+    <row r="69" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A69" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="27">
+      <c r="A70" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+    </row>
+    <row r="71" spans="1:10" customHeight="1" ht="15">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+    </row>
+    <row r="72" spans="1:10" customHeight="1" ht="39">
+      <c r="A72" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A70" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" customHeight="1" ht="27">
-      <c r="A71" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-    </row>
-    <row r="72" spans="1:10" customHeight="1" ht="15">
-      <c r="A72" s="30"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="39">
-      <c r="A73" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="15">
+      <c r="A73" s="32"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="33"/>
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="32"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="32"/>
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="33"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="33"/>
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="2"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
+      <c r="A75" s="32"/>
+      <c r="B75" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
+      <c r="G75" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="32"/>
-      <c r="B76" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="36" t="s">
+        <v>111</v>
+      </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="36" t="s">
-        <v>114</v>
-      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="2"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="B79" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="G79" s="34" t="str">
+        <f>C10</f>
+        <v>Cristell Hernandez Contreras</v>
+      </c>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="2"/>
       <c r="B80" s="34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C80" s="34"/>
       <c r="D80" s="34"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="34" t="str">
-        <f>C10</f>
-        <v>Cristell Hernandez Contreras</v>
+        <f>C12</f>
+        <v>Auxiliar de Supervision</v>
       </c>
       <c r="H80" s="34"/>
       <c r="I80" s="34"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
-      <c r="B81" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="34" t="str">
-        <f>C12</f>
-        <v>Auxiliar de Supervision</v>
-      </c>
-      <c r="H81" s="34"/>
-      <c r="I81" s="34"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="2"/>
@@ -2303,31 +2284,20 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:10" customHeight="1" ht="15">
-      <c r="A84" s="32"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2346,23 +2316,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="G79:I79"/>
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="G80:I80"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="G81:I81"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2492,10 +2462,7 @@
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="H61:I61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H19:I62"/>
+    <mergeCell ref="H19:I61"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/05/2025</t>
+    <t>15/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -95,6 +95,12 @@
     <t>Latitude 5520</t>
   </si>
   <si>
+    <t>FNY9FG3</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>7BV9FG3</t>
   </si>
   <si>
@@ -170,9 +176,6 @@
     <t>Mochila</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Telefono</t>
   </si>
   <si>
@@ -347,10 +350,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Abraham Palayot Sanchez</t>
-  </si>
-  <si>
-    <t>Informacion Financiera</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1203,17 +1206,17 @@
         <v>2</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1224,7 +1227,7 @@
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -1237,299 +1240,251 @@
         <v>3</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="38">
-        <v>4</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E25" s="38"/>
-      <c r="F25" s="38">
-        <v>368631741364</v>
+      <c r="F25" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="38">
-        <v>6</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38">
-        <v>368631741364</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="38">
-        <v>1929</v>
+        <v>23</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="E27" s="38"/>
-      <c r="F27" s="38">
-        <v>730320922522</v>
+      <c r="F27" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="38">
-        <v>8</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E29" s="38"/>
-      <c r="F29" s="38" t="s">
-        <v>48</v>
+      <c r="F29" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="38">
-        <v>10</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38" t="s">
-        <v>54</v>
+      <c r="F31" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="38">
-        <v>12</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="A33" s="38">
+        <v>8</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="38">
+        <v>1929</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38">
+        <v>730320922522</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="38">
-        <v>13</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38">
-        <v>368631740944</v>
-      </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E35" s="38"/>
-      <c r="F35" s="38">
-        <v>368631740944</v>
+      <c r="F35" s="38" t="s">
+        <v>46</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
       <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="38">
-        <v>15</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
@@ -1540,210 +1495,170 @@
       <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="38">
-        <v>17</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="38">
-        <v>19</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="38">
-        <v>21</v>
-      </c>
-      <c r="B42" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="38">
-        <v>23</v>
-      </c>
-      <c r="B44" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="E45" s="38"/>
-      <c r="F45" s="38" t="s">
-        <v>77</v>
+      <c r="F45" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="38">
-        <v>25</v>
-      </c>
-      <c r="B46" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E47" s="38"/>
-      <c r="F47" s="38" t="s">
-        <v>80</v>
+      <c r="F47" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -1754,7 +1669,7 @@
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
       <c r="D48" s="22" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -1764,533 +1679,1058 @@
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="38">
-        <v>28</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="38">
-        <v>30</v>
-      </c>
-      <c r="B52" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E53" s="38"/>
-      <c r="F53" s="38">
-        <v>368631741367</v>
+      <c r="F53" s="38" t="s">
+        <v>64</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
-      <c r="A54" s="38">
-        <v>32</v>
-      </c>
-      <c r="B54" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38">
-        <v>368631741367</v>
-      </c>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="38" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
-      <c r="A56" s="38">
-        <v>34</v>
-      </c>
-      <c r="B56" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="38" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
+    </row>
+    <row r="57" spans="1:10" customHeight="1" ht="15">
+      <c r="A57" s="38">
+        <v>20</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-    </row>
-    <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
+      <c r="D57" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="38">
-        <v>35</v>
-      </c>
-      <c r="B58" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D58" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
-      <c r="A60" s="38">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+    </row>
+    <row r="61" spans="1:10" customHeight="1" ht="15">
+      <c r="A61" s="38">
+        <v>22</v>
+      </c>
+      <c r="B61" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+    </row>
+    <row r="62" spans="1:10" customHeight="1" ht="15">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+    </row>
+    <row r="63" spans="1:10" customHeight="1" ht="15">
+      <c r="A63" s="38">
+        <v>23</v>
+      </c>
+      <c r="B63" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+    </row>
+    <row r="64" spans="1:10" customHeight="1" ht="15">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+    </row>
+    <row r="65" spans="1:10" customHeight="1" ht="15">
+      <c r="A65" s="38">
+        <v>24</v>
+      </c>
+      <c r="B65" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+    </row>
+    <row r="66" spans="1:10" customHeight="1" ht="15">
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+    </row>
+    <row r="67" spans="1:10" customHeight="1" ht="15">
+      <c r="A67" s="38">
+        <v>25</v>
+      </c>
+      <c r="B67" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+    </row>
+    <row r="68" spans="1:10" customHeight="1" ht="15">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+    </row>
+    <row r="69" spans="1:10" customHeight="1" ht="15">
+      <c r="A69" s="38">
+        <v>26</v>
+      </c>
+      <c r="B69" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="15">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+    </row>
+    <row r="71" spans="1:10" customHeight="1" ht="15">
+      <c r="A71" s="38">
+        <v>27</v>
+      </c>
+      <c r="B71" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+    </row>
+    <row r="72" spans="1:10" customHeight="1" ht="15">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="15">
+      <c r="A73" s="38">
+        <v>28</v>
+      </c>
+      <c r="B73" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+    </row>
+    <row r="74" spans="1:10" customHeight="1" ht="15">
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+    </row>
+    <row r="75" spans="1:10" customHeight="1" ht="15">
+      <c r="A75" s="38">
+        <v>29</v>
+      </c>
+      <c r="B75" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D75" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+    </row>
+    <row r="76" spans="1:10" customHeight="1" ht="15">
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+    </row>
+    <row r="77" spans="1:10" customHeight="1" ht="15">
+      <c r="A77" s="38">
+        <v>30</v>
+      </c>
+      <c r="B77" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+    </row>
+    <row r="78" spans="1:10" customHeight="1" ht="15">
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+    </row>
+    <row r="79" spans="1:10" customHeight="1" ht="15">
+      <c r="A79" s="38">
+        <v>31</v>
+      </c>
+      <c r="B79" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+    </row>
+    <row r="80" spans="1:10" customHeight="1" ht="15">
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+    </row>
+    <row r="81" spans="1:10" customHeight="1" ht="15">
+      <c r="A81" s="38">
+        <v>32</v>
+      </c>
+      <c r="B81" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D81" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38">
+        <v>368631741367</v>
+      </c>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+    </row>
+    <row r="82" spans="1:10" customHeight="1" ht="15">
+      <c r="A82" s="22"/>
+      <c r="B82" s="22"/>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+    </row>
+    <row r="83" spans="1:10" customHeight="1" ht="15">
+      <c r="A83" s="38">
+        <v>33</v>
+      </c>
+      <c r="B83" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38">
+        <v>368631741367</v>
+      </c>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+    </row>
+    <row r="84" spans="1:10" customHeight="1" ht="15">
+      <c r="A84" s="22"/>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
+    </row>
+    <row r="85" spans="1:10" customHeight="1" ht="15">
+      <c r="A85" s="38">
+        <v>34</v>
+      </c>
+      <c r="B85" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G85" s="38"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+    </row>
+    <row r="86" spans="1:10" customHeight="1" ht="15">
+      <c r="A86" s="22"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="22"/>
+    </row>
+    <row r="87" spans="1:10" customHeight="1" ht="15">
+      <c r="A87" s="38">
+        <v>35</v>
+      </c>
+      <c r="B87" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C87" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
+    </row>
+    <row r="88" spans="1:10" customHeight="1" ht="15">
+      <c r="A88" s="22"/>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+    </row>
+    <row r="89" spans="1:10" customHeight="1" ht="15">
+      <c r="A89" s="38">
+        <v>36</v>
+      </c>
+      <c r="B89" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G89" s="38"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="38"/>
+    </row>
+    <row r="90" spans="1:10" customHeight="1" ht="15">
+      <c r="A90" s="22"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="22"/>
+    </row>
+    <row r="91" spans="1:10" customHeight="1" ht="15">
+      <c r="A91" s="38">
         <v>37</v>
       </c>
-      <c r="B60" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="38" t="s">
+      <c r="B91" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D91" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G91" s="38"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="38"/>
+    </row>
+    <row r="92" spans="1:10" customHeight="1" ht="15">
+      <c r="A92" s="22"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+    </row>
+    <row r="93" spans="1:10" customHeight="1" ht="15">
+      <c r="A93" s="38">
+        <v>38</v>
+      </c>
+      <c r="B93" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-    </row>
-    <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22" t="s">
+      <c r="D93" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-    </row>
-    <row r="62" spans="1:10" customHeight="1" ht="15">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="24"/>
-    </row>
-    <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="25"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-    </row>
-    <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="26" t="s">
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38"/>
+    </row>
+    <row r="94" spans="1:10" customHeight="1" ht="15">
+      <c r="A94" s="22"/>
+      <c r="B94" s="22"/>
+      <c r="C94" s="22"/>
+      <c r="D94" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-    </row>
-    <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="27"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-    </row>
-    <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="28" t="s">
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
+    </row>
+    <row r="95" spans="1:10" customHeight="1" ht="15">
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
+    </row>
+    <row r="96" spans="1:10" customHeight="1" ht="15">
+      <c r="A96" s="25"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="25"/>
+    </row>
+    <row r="97" spans="1:10" customHeight="1" ht="15">
+      <c r="A97" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
-    </row>
-    <row r="67" spans="1:10" customHeight="1" ht="15">
-      <c r="A67" s="28" t="s">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+    </row>
+    <row r="98" spans="1:10" customHeight="1" ht="15">
+      <c r="A98" s="27"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="27"/>
+    </row>
+    <row r="99" spans="1:10" customHeight="1" ht="15">
+      <c r="A99" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-    </row>
-    <row r="68" spans="1:10" customHeight="1" ht="15">
-      <c r="A68" s="28" t="s">
+      <c r="B99" s="28"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="28"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="28"/>
+    </row>
+    <row r="100" spans="1:10" customHeight="1" ht="15">
+      <c r="A100" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-    </row>
-    <row r="69" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A69" s="29" t="s">
+      <c r="B100" s="28"/>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="28"/>
+      <c r="I100" s="28"/>
+    </row>
+    <row r="101" spans="1:10" customHeight="1" ht="15">
+      <c r="A101" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="27">
-      <c r="A70" s="28" t="s">
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="28"/>
+    </row>
+    <row r="102" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A102" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-    </row>
-    <row r="71" spans="1:10" customHeight="1" ht="15">
-      <c r="A71" s="30"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-    </row>
-    <row r="72" spans="1:10" customHeight="1" ht="39">
-      <c r="A72" s="31" t="s">
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="29"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="29"/>
+      <c r="H102" s="29"/>
+      <c r="I102" s="29"/>
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="1:10" customHeight="1" ht="27">
+      <c r="A103" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="15">
-      <c r="A73" s="32"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
-    </row>
-    <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="2"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-    </row>
-    <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="32"/>
-      <c r="B75" s="34" t="s">
+      <c r="B103" s="28"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+    </row>
+    <row r="104" spans="1:10" customHeight="1" ht="15">
+      <c r="A104" s="30"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="30"/>
+    </row>
+    <row r="105" spans="1:10" customHeight="1" ht="39">
+      <c r="A105" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="35" t="s">
+      <c r="B105" s="31"/>
+      <c r="C105" s="31"/>
+      <c r="D105" s="31"/>
+      <c r="E105" s="31"/>
+      <c r="F105" s="31"/>
+      <c r="G105" s="31"/>
+      <c r="H105" s="31"/>
+      <c r="I105" s="31"/>
+    </row>
+    <row r="106" spans="1:10" customHeight="1" ht="15">
+      <c r="A106" s="32"/>
+      <c r="B106" s="32"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="33"/>
+      <c r="H106" s="33"/>
+      <c r="I106" s="33"/>
+    </row>
+    <row r="107" spans="1:10" customHeight="1" ht="15">
+      <c r="A107" s="2"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="33"/>
+      <c r="I107" s="33"/>
+    </row>
+    <row r="108" spans="1:10" customHeight="1" ht="15">
+      <c r="A108" s="32"/>
+      <c r="B108" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-    </row>
-    <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="36" t="s">
+      <c r="C108" s="34"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-    </row>
-    <row r="77" spans="1:10" customHeight="1" ht="15">
-      <c r="A77" s="2"/>
-      <c r="B77" s="37"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-    </row>
-    <row r="78" spans="1:10" customHeight="1" ht="15">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="1:10" customHeight="1" ht="15">
-      <c r="A79" s="2"/>
-      <c r="B79" s="34" t="s">
+      <c r="H108" s="35"/>
+      <c r="I108" s="35"/>
+    </row>
+    <row r="109" spans="1:10" customHeight="1" ht="15">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="34" t="str">
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+    </row>
+    <row r="110" spans="1:10" customHeight="1" ht="15">
+      <c r="A110" s="2"/>
+      <c r="B110" s="37"/>
+      <c r="C110" s="37"/>
+      <c r="D110" s="37"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="37"/>
+      <c r="H110" s="37"/>
+      <c r="I110" s="37"/>
+    </row>
+    <row r="111" spans="1:10" customHeight="1" ht="15">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+    </row>
+    <row r="112" spans="1:10" customHeight="1" ht="15">
+      <c r="A112" s="2"/>
+      <c r="B112" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C112" s="34"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="34" t="str">
         <f>C10</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
-    </row>
-    <row r="80" spans="1:10" customHeight="1" ht="15">
-      <c r="A80" s="2"/>
-      <c r="B80" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="34" t="str">
+      <c r="H112" s="34"/>
+      <c r="I112" s="34"/>
+    </row>
+    <row r="113" spans="1:10" customHeight="1" ht="15">
+      <c r="A113" s="2"/>
+      <c r="B113" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Información Financiera</v>
       </c>
-      <c r="H80" s="34"/>
-      <c r="I80" s="34"/>
-    </row>
-    <row r="81" spans="1:10" customHeight="1" ht="15">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-    </row>
-    <row r="82" spans="1:10" customHeight="1" ht="15">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="32"/>
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+    </row>
+    <row r="114" spans="1:10" customHeight="1" ht="15">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="32"/>
+      <c r="H114" s="32"/>
+      <c r="I114" s="32"/>
+    </row>
+    <row r="115" spans="1:10" customHeight="1" ht="15">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+    </row>
+    <row r="116" spans="1:10" customHeight="1" ht="15">
+      <c r="A116" s="32"/>
+      <c r="B116" s="32"/>
+      <c r="C116" s="32"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2309,23 +2749,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="G113:I113"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2455,7 +2895,106 @@
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H19:I61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H19:I94"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>15/05/2025</t>
+    <t>19/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -98,84 +98,84 @@
     <t>FNY9FG3</t>
   </si>
   <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Docking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>7BV9FG3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00050</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>Optiplex 3050</t>
-  </si>
-  <si>
-    <t>9NK8CM2</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00079</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>3W9J0C3</t>
-  </si>
-  <si>
-    <t>Cargador de Docking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>ACTECK</t>
-  </si>
-  <si>
-    <t>MK450</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>6W69G04</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216R</t>
-  </si>
-  <si>
-    <t>23-08-29697</t>
-  </si>
-  <si>
-    <t>Mochila</t>
-  </si>
-  <si>
     <t>Telefono</t>
   </si>
   <si>
@@ -350,10 +350,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Fernando de Jesus Culebro Hernandez</t>
+  </si>
+  <si>
+    <t>Supervisor Operaciones</t>
   </si>
 </sst>
 </file>
@@ -1189,238 +1189,278 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="38">
-        <v>2</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="38" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" customHeight="1" ht="15">
+      <c r="A22" s="38">
+        <v>3</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-    </row>
-    <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="D22" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="38">
-        <v>3</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="38" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="15">
+      <c r="A24" s="38">
+        <v>4</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="D24" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
       <c r="A25" s="38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
+      <c r="A26" s="38">
+        <v>6</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38">
+        <v>368631741364</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
       <c r="A27" s="38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27" s="38"/>
-      <c r="F27" s="38" t="s">
-        <v>38</v>
+      <c r="F27" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="A28" s="38">
+        <v>8</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="38">
+        <v>1929</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38">
+        <v>730320922522</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
       <c r="A29" s="38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E29" s="38"/>
-      <c r="F29" s="38">
-        <v>368631741364</v>
+      <c r="F29" s="38" t="s">
+        <v>45</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
+      <c r="A30" s="38">
+        <v>10</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="38">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38">
-        <v>368631741364</v>
+      <c r="F31" s="38" t="s">
+        <v>51</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
+      <c r="A32" s="38">
+        <v>12</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="38">
-        <v>1929</v>
+        <v>57</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>58</v>
       </c>
       <c r="E33" s="38"/>
-      <c r="F33" s="38">
-        <v>730320922522</v>
+      <c r="F33" s="38" t="s">
+        <v>59</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1431,7 +1471,7 @@
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -1441,394 +1481,474 @@
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E35" s="38"/>
-      <c r="F35" s="38" t="s">
-        <v>46</v>
+      <c r="F35" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
       <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
+      <c r="A36" s="38">
+        <v>15</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38">
+        <v>368631740944</v>
+      </c>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="38">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="38" t="s">
-        <v>48</v>
-      </c>
       <c r="D37" s="38" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
+      <c r="A38" s="38">
+        <v>17</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="38">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="22"/>
+      <c r="A40" s="38">
+        <v>19</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="38">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
+      <c r="A42" s="38">
+        <v>21</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="38">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
+      <c r="A44" s="38">
+        <v>23</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="38">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="E45" s="38"/>
-      <c r="F45" s="38">
-        <v>368631740944</v>
+      <c r="F45" s="38" t="s">
+        <v>75</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
+      <c r="A46" s="38">
+        <v>25</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="38">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E47" s="38"/>
-      <c r="F47" s="38">
-        <v>368631740944</v>
+      <c r="F47" s="38" t="s">
+        <v>79</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
+      <c r="A48" s="38">
+        <v>27</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="38">
-        <v>16</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D49" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
+      <c r="A50" s="38">
+        <v>28</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
+      <c r="A52" s="38">
+        <v>30</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
+      <c r="A54" s="38">
+        <v>32</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38">
+        <v>368631741367</v>
+      </c>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="38">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="38" t="s">
-        <v>23</v>
-      </c>
       <c r="D55" s="38" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38" t="s">
-        <v>66</v>
+      <c r="F55" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
+      <c r="A56" s="38">
+        <v>34</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
       <c r="A57" s="38">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C57" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="38" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -1839,7 +1959,7 @@
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
       <c r="D58" s="22" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -1849,54 +1969,62 @@
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
-      <c r="A60" s="22"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
+      <c r="A60" s="38">
+        <v>37</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C60" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
       <c r="A61" s="38">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G61" s="38"/>
       <c r="H61" s="38"/>
@@ -1907,7 +2035,7 @@
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
       <c r="D62" s="22" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
@@ -1916,821 +2044,277 @@
       <c r="I62" s="22"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="38">
-        <v>23</v>
-      </c>
-      <c r="B63" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C63" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="38">
-        <v>24</v>
-      </c>
-      <c r="B65" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C65" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
+      <c r="A65" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
+      <c r="A66" s="27"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="27"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
-      <c r="A67" s="38">
-        <v>25</v>
-      </c>
-      <c r="B67" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C67" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D67" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
+      <c r="A67" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
+      <c r="A68" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="28"/>
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
-      <c r="A69" s="38">
-        <v>26</v>
-      </c>
-      <c r="B69" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C69" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D69" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E69" s="38"/>
-      <c r="F69" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="15">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-    </row>
-    <row r="71" spans="1:10" customHeight="1" ht="15">
-      <c r="A71" s="38">
-        <v>27</v>
-      </c>
-      <c r="B71" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D71" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
+      <c r="A69" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A70" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="1:10" customHeight="1" ht="27">
+      <c r="A71" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
     </row>
     <row r="72" spans="1:10" customHeight="1" ht="15">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="15">
-      <c r="A73" s="38">
-        <v>28</v>
-      </c>
-      <c r="B73" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D73" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="39">
+      <c r="A73" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="31"/>
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="38">
-        <v>29</v>
-      </c>
-      <c r="B75" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D75" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="33"/>
+      <c r="I75" s="33"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="22"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
+      <c r="A76" s="32"/>
+      <c r="B76" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="34"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
-      <c r="A77" s="38">
-        <v>30</v>
-      </c>
-      <c r="B77" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
-      <c r="A79" s="38">
-        <v>31</v>
-      </c>
-      <c r="B79" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D79" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-    </row>
-    <row r="81" spans="1:10" customHeight="1" ht="15">
-      <c r="A81" s="38">
-        <v>32</v>
-      </c>
-      <c r="B81" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D81" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38">
-        <v>368631741367</v>
-      </c>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-    </row>
-    <row r="82" spans="1:10" customHeight="1" ht="15">
-      <c r="A82" s="22"/>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="22"/>
-    </row>
-    <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="38">
-        <v>33</v>
-      </c>
-      <c r="B83" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C83" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38">
-        <v>368631741367</v>
-      </c>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-    </row>
-    <row r="84" spans="1:10" customHeight="1" ht="15">
-      <c r="A84" s="22"/>
-      <c r="B84" s="22"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="22"/>
-    </row>
-    <row r="85" spans="1:10" customHeight="1" ht="15">
-      <c r="A85" s="38">
-        <v>34</v>
-      </c>
-      <c r="B85" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C85" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D85" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-    </row>
-    <row r="86" spans="1:10" customHeight="1" ht="15">
-      <c r="A86" s="22"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
-      <c r="G86" s="22"/>
-      <c r="H86" s="22"/>
-      <c r="I86" s="22"/>
-    </row>
-    <row r="87" spans="1:10" customHeight="1" ht="15">
-      <c r="A87" s="38">
-        <v>35</v>
-      </c>
-      <c r="B87" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C87" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38"/>
-    </row>
-    <row r="88" spans="1:10" customHeight="1" ht="15">
-      <c r="A88" s="22"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="22"/>
-      <c r="H88" s="22"/>
-      <c r="I88" s="22"/>
-    </row>
-    <row r="89" spans="1:10" customHeight="1" ht="15">
-      <c r="A89" s="38">
-        <v>36</v>
-      </c>
-      <c r="B89" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38"/>
-    </row>
-    <row r="90" spans="1:10" customHeight="1" ht="15">
-      <c r="A90" s="22"/>
-      <c r="B90" s="22"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E90" s="22"/>
-      <c r="F90" s="22"/>
-      <c r="G90" s="22"/>
-      <c r="H90" s="22"/>
-      <c r="I90" s="22"/>
-    </row>
-    <row r="91" spans="1:10" customHeight="1" ht="15">
-      <c r="A91" s="38">
-        <v>37</v>
-      </c>
-      <c r="B91" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C91" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="G91" s="38"/>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38"/>
-    </row>
-    <row r="92" spans="1:10" customHeight="1" ht="15">
-      <c r="A92" s="22"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-      <c r="I92" s="22"/>
-    </row>
-    <row r="93" spans="1:10" customHeight="1" ht="15">
-      <c r="A93" s="38">
-        <v>38</v>
-      </c>
-      <c r="B93" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C93" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D93" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-    </row>
-    <row r="94" spans="1:10" customHeight="1" ht="15">
-      <c r="A94" s="22"/>
-      <c r="B94" s="22"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-      <c r="G94" s="22"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="22"/>
-    </row>
-    <row r="95" spans="1:10" customHeight="1" ht="15">
-      <c r="A95" s="16"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
-      <c r="E95" s="16"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
-      <c r="H95" s="24"/>
-      <c r="I95" s="24"/>
-    </row>
-    <row r="96" spans="1:10" customHeight="1" ht="15">
-      <c r="A96" s="25"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="25"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="25"/>
-    </row>
-    <row r="97" spans="1:10" customHeight="1" ht="15">
-      <c r="A97" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-      <c r="H97" s="26"/>
-      <c r="I97" s="26"/>
-    </row>
-    <row r="98" spans="1:10" customHeight="1" ht="15">
-      <c r="A98" s="27"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
-      <c r="D98" s="27"/>
-      <c r="E98" s="27"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="27"/>
-      <c r="H98" s="27"/>
-      <c r="I98" s="27"/>
-    </row>
-    <row r="99" spans="1:10" customHeight="1" ht="15">
-      <c r="A99" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B99" s="28"/>
-      <c r="C99" s="28"/>
-      <c r="D99" s="28"/>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="28"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="28"/>
-    </row>
-    <row r="100" spans="1:10" customHeight="1" ht="15">
-      <c r="A100" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B100" s="28"/>
-      <c r="C100" s="28"/>
-      <c r="D100" s="28"/>
-      <c r="E100" s="28"/>
-      <c r="F100" s="28"/>
-      <c r="G100" s="28"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="28"/>
-    </row>
-    <row r="101" spans="1:10" customHeight="1" ht="15">
-      <c r="A101" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B101" s="28"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="28"/>
-    </row>
-    <row r="102" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A102" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
-      <c r="E102" s="29"/>
-      <c r="F102" s="29"/>
-      <c r="G102" s="29"/>
-      <c r="H102" s="29"/>
-      <c r="I102" s="29"/>
-      <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="1:10" customHeight="1" ht="27">
-      <c r="A103" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="B103" s="28"/>
-      <c r="C103" s="28"/>
-      <c r="D103" s="28"/>
-      <c r="E103" s="28"/>
-      <c r="F103" s="28"/>
-      <c r="G103" s="28"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="28"/>
-    </row>
-    <row r="104" spans="1:10" customHeight="1" ht="15">
-      <c r="A104" s="30"/>
-      <c r="B104" s="30"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="30"/>
-    </row>
-    <row r="105" spans="1:10" customHeight="1" ht="39">
-      <c r="A105" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105" s="31"/>
-      <c r="C105" s="31"/>
-      <c r="D105" s="31"/>
-      <c r="E105" s="31"/>
-      <c r="F105" s="31"/>
-      <c r="G105" s="31"/>
-      <c r="H105" s="31"/>
-      <c r="I105" s="31"/>
-    </row>
-    <row r="106" spans="1:10" customHeight="1" ht="15">
-      <c r="A106" s="32"/>
-      <c r="B106" s="32"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="32"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="33"/>
-      <c r="H106" s="33"/>
-      <c r="I106" s="33"/>
-    </row>
-    <row r="107" spans="1:10" customHeight="1" ht="15">
-      <c r="A107" s="2"/>
-      <c r="B107" s="32"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="33"/>
-      <c r="I107" s="33"/>
-    </row>
-    <row r="108" spans="1:10" customHeight="1" ht="15">
-      <c r="A108" s="32"/>
-      <c r="B108" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C108" s="34"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="H108" s="35"/>
-      <c r="I108" s="35"/>
-    </row>
-    <row r="109" spans="1:10" customHeight="1" ht="15">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-    </row>
-    <row r="110" spans="1:10" customHeight="1" ht="15">
-      <c r="A110" s="2"/>
-      <c r="B110" s="37"/>
-      <c r="C110" s="37"/>
-      <c r="D110" s="37"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="37"/>
-      <c r="H110" s="37"/>
-      <c r="I110" s="37"/>
-    </row>
-    <row r="111" spans="1:10" customHeight="1" ht="15">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-    </row>
-    <row r="112" spans="1:10" customHeight="1" ht="15">
-      <c r="A112" s="2"/>
-      <c r="B112" s="34" t="s">
+      <c r="A80" s="2"/>
+      <c r="B80" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="C112" s="34"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="34" t="str">
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="34" t="str">
         <f>C10</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="H112" s="34"/>
-      <c r="I112" s="34"/>
-    </row>
-    <row r="113" spans="1:10" customHeight="1" ht="15">
-      <c r="A113" s="2"/>
-      <c r="B113" s="34" t="s">
+      <c r="H80" s="34"/>
+      <c r="I80" s="34"/>
+    </row>
+    <row r="81" spans="1:10" customHeight="1" ht="15">
+      <c r="A81" s="2"/>
+      <c r="B81" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="34" t="str">
+      <c r="C81" s="34"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Información Financiera</v>
       </c>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-    </row>
-    <row r="114" spans="1:10" customHeight="1" ht="15">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="32"/>
-      <c r="H114" s="32"/>
-      <c r="I114" s="32"/>
-    </row>
-    <row r="115" spans="1:10" customHeight="1" ht="15">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-    </row>
-    <row r="116" spans="1:10" customHeight="1" ht="15">
-      <c r="A116" s="32"/>
-      <c r="B116" s="32"/>
-      <c r="C116" s="32"/>
-      <c r="D116" s="32"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="34"/>
+    </row>
+    <row r="82" spans="1:10" customHeight="1" ht="15">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+    </row>
+    <row r="83" spans="1:10" customHeight="1" ht="15">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:10" customHeight="1" ht="15">
+      <c r="A84" s="32"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2749,23 +2333,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="A97:I97"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A103:I103"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A105:I105"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="G112:I112"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="G81:I81"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2898,103 +2482,7 @@
     <mergeCell ref="D62:E62"/>
     <mergeCell ref="F62:G62"/>
     <mergeCell ref="H62:I62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="H19:I94"/>
+    <mergeCell ref="H19:I62"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>19/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -95,7 +95,7 @@
     <t>Latitude 5520</t>
   </si>
   <si>
-    <t>FNY9FG3</t>
+    <t>1446MG00C698</t>
   </si>
   <si>
     <t>7BV9FG3</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Fernando de Jesus Culebro Hernandez</t>
-  </si>
-  <si>
-    <t>Supervisor Operaciones</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="111">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>02/06/2025</t>
+    <t>09/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>1446MG00C698</t>
   </si>
   <si>
     <t>7BV9FG3</t>
@@ -1189,89 +1186,89 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="B21" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="D21" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" customHeight="1" ht="15">
+      <c r="A23" s="38">
         <v>3</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="38" t="s">
+      <c r="B23" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-    </row>
-    <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
+      <c r="D23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
         <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1282,17 +1279,17 @@
         <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E25" s="38"/>
-      <c r="F25" s="38" t="s">
-        <v>37</v>
+      <c r="F25" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1303,13 +1300,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="D26" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38">
@@ -1324,17 +1321,17 @@
         <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>40</v>
+      <c r="D27" s="38">
+        <v>1929</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38">
-        <v>368631741364</v>
+        <v>730320922522</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1345,17 +1342,17 @@
         <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="38">
-        <v>1929</v>
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>43</v>
       </c>
       <c r="E28" s="38"/>
-      <c r="F28" s="38">
-        <v>730320922522</v>
+      <c r="F28" s="38" t="s">
+        <v>44</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1366,17 +1363,17 @@
         <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1387,17 +1384,17 @@
         <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1408,17 +1405,17 @@
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1429,68 +1426,68 @@
         <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="38">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="38">
         <v>13</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
+      <c r="B34" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38">
+        <v>368631740944</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="38">
         <v>14</v>
       </c>
       <c r="B35" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="D35" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -1505,17 +1502,17 @@
         <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>368631740944</v>
+      <c r="F36" s="38" t="s">
+        <v>61</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1526,17 +1523,17 @@
         <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="D37" s="38" t="s">
         <v>47</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>61</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1547,17 +1544,17 @@
         <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1568,17 +1565,17 @@
         <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1589,17 +1586,17 @@
         <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1610,17 +1607,17 @@
         <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1631,17 +1628,17 @@
         <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1652,13 +1649,13 @@
         <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
@@ -1673,13 +1670,13 @@
         <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C44" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
@@ -1694,17 +1691,17 @@
         <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1715,13 +1712,13 @@
         <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
@@ -1736,72 +1733,72 @@
         <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="38">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="38">
         <v>27</v>
       </c>
-      <c r="B48" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="38" t="s">
+      <c r="B49" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="38">
         <v>28</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C50" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
@@ -1812,13 +1809,13 @@
         <v>29</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C51" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
@@ -1833,17 +1830,17 @@
         <v>30</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -1854,17 +1851,17 @@
         <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E53" s="38"/>
-      <c r="F53" s="38" t="s">
-        <v>51</v>
+      <c r="F53" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -1875,13 +1872,13 @@
         <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C54" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38">
@@ -1896,17 +1893,17 @@
         <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38">
-        <v>368631741367</v>
+      <c r="F55" s="38" t="s">
+        <v>87</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1917,13 +1914,13 @@
         <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="38" t="s">
@@ -1934,55 +1931,55 @@
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="38">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+    </row>
+    <row r="58" spans="1:10" customHeight="1" ht="15">
+      <c r="A58" s="38">
         <v>35</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C57" s="38" t="s">
+      <c r="B58" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-    </row>
-    <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="22"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
+      <c r="D58" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
       <c r="A59" s="38">
         <v>36</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -1993,13 +1990,13 @@
         <v>37</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
@@ -2010,84 +2007,76 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="38">
-        <v>38</v>
-      </c>
-      <c r="B61" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D61" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22" t="s">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+    </row>
+    <row r="63" spans="1:10" customHeight="1" ht="15">
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+    </row>
+    <row r="64" spans="1:10" customHeight="1" ht="15">
+      <c r="A64" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-    </row>
-    <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
-    </row>
-    <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="26" t="s">
+      <c r="A65" s="27"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="27"/>
+    </row>
+    <row r="66" spans="1:10" customHeight="1" ht="15">
+      <c r="A66" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-    </row>
-    <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="27"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
       <c r="A67" s="28" t="s">
@@ -2115,141 +2104,144 @@
       <c r="H68" s="28"/>
       <c r="I68" s="28"/>
     </row>
-    <row r="69" spans="1:10" customHeight="1" ht="15">
-      <c r="A69" s="28" t="s">
+    <row r="69" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A69" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A70" s="29" t="s">
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="27">
+      <c r="A70" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" customHeight="1" ht="27">
-      <c r="A71" s="28" t="s">
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+    </row>
+    <row r="71" spans="1:10" customHeight="1" ht="15">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+    </row>
+    <row r="72" spans="1:10" customHeight="1" ht="39">
+      <c r="A72" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-    </row>
-    <row r="72" spans="1:10" customHeight="1" ht="15">
-      <c r="A72" s="30"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="39">
-      <c r="A73" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="15">
+      <c r="A73" s="32"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="33"/>
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="32"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="32"/>
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="33"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="33"/>
       <c r="I74" s="33"/>
     </row>
     <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="2"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
+      <c r="A75" s="32"/>
+      <c r="B75" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
+      <c r="G75" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="32"/>
-      <c r="B76" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="36" t="s">
+        <v>108</v>
+      </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="36" t="s">
-        <v>109</v>
-      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="2"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="B79" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="G79" s="34" t="str">
+        <f>C10</f>
+        <v>Cristell Hernandez Contreras</v>
+      </c>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="2"/>
@@ -2261,27 +2253,22 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="34" t="str">
-        <f>C10</f>
-        <v>Cristell Hernandez Contreras</v>
+        <f>C12</f>
+        <v>Coordinador de Información Financiera</v>
       </c>
       <c r="H80" s="34"/>
       <c r="I80" s="34"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
-      <c r="B81" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="34" t="str">
-        <f>C12</f>
-        <v>Coordinador de Información Financiera</v>
-      </c>
-      <c r="H81" s="34"/>
-      <c r="I81" s="34"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="2"/>
@@ -2290,31 +2277,20 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:10" customHeight="1" ht="15">
-      <c r="A84" s="32"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2333,23 +2309,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="G79:I79"/>
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="G80:I80"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="G81:I81"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2479,10 +2455,7 @@
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="H61:I61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H19:I62"/>
+    <mergeCell ref="H19:I61"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>09/06/2025</t>
+    <t>12/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -95,6 +95,9 @@
     <t>Latitude 5520</t>
   </si>
   <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
     <t>7BV9FG3</t>
   </si>
   <si>
@@ -113,6 +116,15 @@
     <t>DVZ-VH-TI-00079</t>
   </si>
   <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
     <t>Docking Station</t>
   </si>
   <si>
@@ -290,13 +302,13 @@
     <t>DVZ-VH-TI-00076</t>
   </si>
   <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>2131LZD121R8</t>
   </si>
   <si>
     <t>Pantalla TV</t>
@@ -315,6 +327,15 @@
   </si>
   <si>
     <t>DVZ-VH-TI-00117</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>vybuhniok</t>
+  </si>
+  <si>
+    <t>Y8VBUNIOMP</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1186,89 +1207,89 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="38">
-        <v>2</v>
-      </c>
-      <c r="B21" s="38" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" customHeight="1" ht="15">
+      <c r="A22" s="38">
+        <v>3</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
+      <c r="D22" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-    </row>
-    <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="38">
-        <v>3</v>
-      </c>
-      <c r="B23" s="38" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="38">
         <v>4</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1279,17 +1300,17 @@
         <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38">
-        <v>368631741364</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1300,17 +1321,17 @@
         <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="38"/>
-      <c r="F26" s="38">
-        <v>368631741364</v>
+      <c r="F26" s="38" t="s">
+        <v>40</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1321,17 +1342,17 @@
         <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="38">
-        <v>1929</v>
+        <v>42</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>43</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38">
-        <v>730320922522</v>
+        <v>368631741364</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1342,17 +1363,17 @@
         <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="38" t="s">
         <v>42</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
         <v>43</v>
       </c>
       <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
-        <v>44</v>
+      <c r="F28" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1363,17 +1384,17 @@
         <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>47</v>
+      <c r="D29" s="38">
+        <v>1929</v>
       </c>
       <c r="E29" s="38"/>
-      <c r="F29" s="38" t="s">
-        <v>48</v>
+      <c r="F29" s="38">
+        <v>730320922522</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1384,17 +1405,17 @@
         <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1405,17 +1426,17 @@
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="38" t="s">
         <v>51</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>53</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1426,93 +1447,93 @@
         <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
+      <c r="A33" s="38">
+        <v>13</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E34" s="38"/>
-      <c r="F34" s="38">
-        <v>368631740944</v>
+      <c r="F34" s="38" t="s">
+        <v>62</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="38">
-        <v>14</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38">
-        <v>368631740944</v>
-      </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
         <v>15</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>61</v>
+      <c r="F36" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1523,17 +1544,17 @@
         <v>16</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E37" s="38"/>
-      <c r="F37" s="38" t="s">
-        <v>50</v>
+      <c r="F37" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
@@ -1544,17 +1565,17 @@
         <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1565,17 +1586,17 @@
         <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1586,7 +1607,7 @@
         <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>23</v>
@@ -1607,10 +1628,10 @@
         <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D41" s="38" t="s">
         <v>68</v>
@@ -1628,17 +1649,17 @@
         <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C42" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="38" t="s">
         <v>70</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>71</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1649,13 +1670,13 @@
         <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
@@ -1670,17 +1691,17 @@
         <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G44" s="38"/>
       <c r="H44" s="38"/>
@@ -1691,13 +1712,13 @@
         <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
@@ -1712,13 +1733,13 @@
         <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
@@ -1736,90 +1757,90 @@
         <v>55</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
+      <c r="A48" s="38">
+        <v>27</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="38">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C49" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="38">
-        <v>28</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
         <v>29</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
@@ -1830,17 +1851,17 @@
         <v>30</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="38" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="38"/>
@@ -1851,17 +1872,17 @@
         <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E53" s="38"/>
-      <c r="F53" s="38">
-        <v>368631741367</v>
+      <c r="F53" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -1872,17 +1893,17 @@
         <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E54" s="38"/>
-      <c r="F54" s="38">
-        <v>368631741367</v>
+      <c r="F54" s="38" t="s">
+        <v>54</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -1893,17 +1914,17 @@
         <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38" t="s">
-        <v>87</v>
+      <c r="F55" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1914,47 +1935,55 @@
         <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E56" s="38"/>
-      <c r="F56" s="38" t="s">
-        <v>88</v>
+      <c r="F56" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="22"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
+      <c r="A57" s="38">
+        <v>35</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="15">
       <c r="A58" s="38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C58" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="38" t="s">
@@ -1965,162 +1994,177 @@
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
-      <c r="A59" s="38">
-        <v>36</v>
-      </c>
-      <c r="B59" s="38" t="s">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="D59" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
         <v>37</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="22"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22" t="s">
+      <c r="A61" s="38">
+        <v>38</v>
+      </c>
+      <c r="B61" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
+      <c r="D61" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="24"/>
+      <c r="A62" s="38">
+        <v>39</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="25"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
-      <c r="A64" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
+      <c r="A64" s="38">
+        <v>40</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="27"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
+      <c r="A66" s="25"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
-      <c r="A67" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
+      <c r="A67" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
-      <c r="A68" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-    </row>
-    <row r="69" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A69" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="2"/>
-    </row>
-    <row r="70" spans="1:10" customHeight="1" ht="27">
+      <c r="A68" s="27"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="27"/>
+    </row>
+    <row r="69" spans="1:10" customHeight="1" ht="15">
+      <c r="A69" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+    </row>
+    <row r="70" spans="1:10" customHeight="1" ht="15">
       <c r="A70" s="28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B70" s="28"/>
       <c r="C70" s="28"/>
@@ -2132,132 +2176,129 @@
       <c r="I70" s="28"/>
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
-      <c r="A71" s="30"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-    </row>
-    <row r="72" spans="1:10" customHeight="1" ht="39">
-      <c r="A72" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="15">
-      <c r="A73" s="32"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
+      <c r="A71" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
+    </row>
+    <row r="72" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A72" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="27">
+      <c r="A73" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" s="28"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
     </row>
     <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="2"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-    </row>
-    <row r="75" spans="1:10" customHeight="1" ht="15">
-      <c r="A75" s="32"/>
-      <c r="B75" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+    </row>
+    <row r="75" spans="1:10" customHeight="1" ht="39">
+      <c r="A75" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="36" t="s">
-        <v>108</v>
-      </c>
+      <c r="A76" s="32"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
+      <c r="G76" s="33"/>
+      <c r="H76" s="33"/>
+      <c r="I76" s="33"/>
     </row>
     <row r="77" spans="1:10" customHeight="1" ht="15">
       <c r="A77" s="2"/>
-      <c r="B77" s="37"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="33"/>
+      <c r="I77" s="33"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
+      <c r="G78" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="H78" s="35"/>
+      <c r="I78" s="35"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="2"/>
-      <c r="B79" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="36" t="s">
+        <v>115</v>
+      </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
-      <c r="G79" s="34" t="str">
-        <f>C10</f>
-        <v>Cristell Hernandez Contreras</v>
-      </c>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
       <c r="A80" s="2"/>
-      <c r="B80" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="34" t="str">
-        <f>C12</f>
-        <v>Coordinador de Información Financiera</v>
-      </c>
-      <c r="H80" s="34"/>
-      <c r="I80" s="34"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
@@ -2266,31 +2307,74 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="B82" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
+      <c r="G82" s="34" t="str">
+        <f>C10</f>
+        <v>Cristell Hernandez Contreras</v>
+      </c>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
     </row>
     <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="32"/>
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
+      <c r="G83" s="34" t="str">
+        <f>C12</f>
+        <v>Coordinador de Información Financiera</v>
+      </c>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+    </row>
+    <row r="84" spans="1:10" customHeight="1" ht="15">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+    </row>
+    <row r="85" spans="1:10" customHeight="1" ht="15">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:10" customHeight="1" ht="15">
+      <c r="A86" s="32"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2309,23 +2393,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="H65:I65"/>
     <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="G83:I83"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2455,7 +2539,16 @@
     <mergeCell ref="D61:E61"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H19:I61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H19:I64"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="122">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>12/06/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -116,6 +116,27 @@
     <t>DVZ-VH-TI-00079</t>
   </si>
   <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>2131LZD121R8</t>
+  </si>
+  <si>
     <t>Cargador de Laptop</t>
   </si>
   <si>
@@ -143,18 +164,12 @@
     <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
   </si>
   <si>
-    <t>Teclado</t>
-  </si>
-  <si>
     <t>ACTECK</t>
   </si>
   <si>
     <t>MK450</t>
   </si>
   <si>
-    <t>Mouse</t>
-  </si>
-  <si>
     <t>Microsoft</t>
   </si>
   <si>
@@ -302,13 +317,10 @@
     <t>DVZ-VH-TI-00076</t>
   </si>
   <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2131LZD121R8</t>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
     <t>Pantalla TV</t>
@@ -368,10 +380,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1282,14 +1294,14 @@
         <v>32</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1300,17 +1312,17 @@
         <v>5</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1321,17 +1333,17 @@
         <v>6</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1342,17 +1354,17 @@
         <v>7</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
         <v>43</v>
       </c>
       <c r="E27" s="38"/>
-      <c r="F27" s="38">
-        <v>368631741364</v>
+      <c r="F27" s="38" t="s">
+        <v>44</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1363,17 +1375,17 @@
         <v>8</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E28" s="38"/>
-      <c r="F28" s="38">
-        <v>368631741364</v>
+      <c r="F28" s="38" t="s">
+        <v>47</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1384,17 +1396,17 @@
         <v>9</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="38">
-        <v>1929</v>
+        <v>48</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>49</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38">
-        <v>730320922522</v>
+        <v>368631741364</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1405,17 +1417,17 @@
         <v>10</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>48</v>
+      <c r="F30" s="38">
+        <v>368631741364</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1426,17 +1438,17 @@
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C31" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="38" t="s">
-        <v>51</v>
+      <c r="D31" s="38">
+        <v>1929</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38" t="s">
-        <v>52</v>
+      <c r="F31" s="38">
+        <v>730320922522</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1447,17 +1459,17 @@
         <v>12</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1468,17 +1480,17 @@
         <v>13</v>
       </c>
       <c r="B33" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="D33" s="38" t="s">
         <v>56</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>57</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1489,93 +1501,93 @@
         <v>14</v>
       </c>
       <c r="B34" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="38" t="s">
-        <v>60</v>
-      </c>
       <c r="D34" s="38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22" t="s">
+      <c r="A35" s="38">
+        <v>15</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
       <c r="A36" s="38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E36" s="38"/>
-      <c r="F36" s="38">
-        <v>368631740944</v>
+      <c r="F36" s="38" t="s">
+        <v>67</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="38">
-        <v>16</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38">
-        <v>368631740944</v>
-      </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="38">
         <v>17</v>
       </c>
       <c r="B38" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>64</v>
-      </c>
       <c r="E38" s="38"/>
-      <c r="F38" s="38" t="s">
-        <v>65</v>
+      <c r="F38" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -1586,17 +1598,17 @@
         <v>18</v>
       </c>
       <c r="B39" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="38" t="s">
-        <v>51</v>
-      </c>
       <c r="E39" s="38"/>
-      <c r="F39" s="38" t="s">
-        <v>54</v>
+      <c r="F39" s="38">
+        <v>368631740944</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
@@ -1607,17 +1619,17 @@
         <v>19</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
@@ -1628,17 +1640,17 @@
         <v>20</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
@@ -1649,17 +1661,17 @@
         <v>21</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G42" s="38"/>
       <c r="H42" s="38"/>
@@ -1670,17 +1682,17 @@
         <v>22</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G43" s="38"/>
       <c r="H43" s="38"/>
@@ -1691,10 +1703,10 @@
         <v>23</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>75</v>
@@ -1712,17 +1724,17 @@
         <v>24</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -1733,17 +1745,17 @@
         <v>25</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
@@ -1754,17 +1766,17 @@
         <v>26</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G47" s="38"/>
       <c r="H47" s="38"/>
@@ -1775,17 +1787,17 @@
         <v>27</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="38"/>
@@ -1796,93 +1808,93 @@
         <v>28</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G49" s="38"/>
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
+      <c r="A50" s="38">
+        <v>29</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="38">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C51" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="38">
-        <v>30</v>
-      </c>
-      <c r="B52" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
       <c r="A53" s="38">
         <v>31</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C53" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G53" s="38"/>
       <c r="H53" s="38"/>
@@ -1893,17 +1905,17 @@
         <v>32</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="38" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="G54" s="38"/>
       <c r="H54" s="38"/>
@@ -1914,17 +1926,17 @@
         <v>33</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="E55" s="38"/>
-      <c r="F55" s="38">
-        <v>368631741367</v>
+      <c r="F55" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
@@ -1935,17 +1947,17 @@
         <v>34</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E56" s="38"/>
-      <c r="F56" s="38">
-        <v>368631741367</v>
+      <c r="F56" s="38" t="s">
+        <v>59</v>
       </c>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
@@ -1956,17 +1968,17 @@
         <v>35</v>
       </c>
       <c r="B57" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C57" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57" s="38" t="s">
-        <v>64</v>
-      </c>
       <c r="E57" s="38"/>
-      <c r="F57" s="38" t="s">
-        <v>91</v>
+      <c r="F57" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
@@ -1977,123 +1989,131 @@
         <v>36</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="E58" s="38"/>
-      <c r="F58" s="38" t="s">
-        <v>92</v>
+      <c r="F58" s="38">
+        <v>368631741367</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="15">
-      <c r="A59" s="22"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
+      <c r="A59" s="38">
+        <v>37</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="15">
       <c r="A60" s="38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="15">
-      <c r="A61" s="38">
-        <v>38</v>
-      </c>
-      <c r="B61" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C61" s="38" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D61" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="15">
       <c r="A62" s="38">
         <v>39</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="15">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22" t="s">
+      <c r="A63" s="38">
+        <v>40</v>
+      </c>
+      <c r="B63" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
+      <c r="D63" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="15">
       <c r="A64" s="38">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D64" s="38" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="38" t="s">
@@ -2104,80 +2124,88 @@
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="1:10" customHeight="1" ht="15">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="24"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
     </row>
     <row r="66" spans="1:10" customHeight="1" ht="15">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
+      <c r="A66" s="38">
+        <v>42</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
     </row>
     <row r="67" spans="1:10" customHeight="1" ht="15">
-      <c r="A67" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="1:10" customHeight="1" ht="15">
-      <c r="A68" s="27"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="1:10" customHeight="1" ht="15">
-      <c r="A69" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
+      <c r="A69" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
     </row>
     <row r="70" spans="1:10" customHeight="1" ht="15">
-      <c r="A70" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
+      <c r="A70" s="27"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
     </row>
     <row r="71" spans="1:10" customHeight="1" ht="15">
       <c r="A71" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B71" s="28"/>
       <c r="C71" s="28"/>
@@ -2188,23 +2216,22 @@
       <c r="H71" s="28"/>
       <c r="I71" s="28"/>
     </row>
-    <row r="72" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A72" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" customHeight="1" ht="27">
+    <row r="72" spans="1:10" customHeight="1" ht="15">
+      <c r="A72" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+    </row>
+    <row r="73" spans="1:10" customHeight="1" ht="15">
       <c r="A73" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B73" s="28"/>
       <c r="C73" s="28"/>
@@ -2215,96 +2242,101 @@
       <c r="H73" s="28"/>
       <c r="I73" s="28"/>
     </row>
-    <row r="74" spans="1:10" customHeight="1" ht="15">
-      <c r="A74" s="30"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-    </row>
-    <row r="75" spans="1:10" customHeight="1" ht="39">
-      <c r="A75" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
+    <row r="74" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A74" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="29"/>
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" spans="1:10" customHeight="1" ht="27">
+      <c r="A75" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
     </row>
     <row r="76" spans="1:10" customHeight="1" ht="15">
-      <c r="A76" s="32"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="33"/>
-    </row>
-    <row r="77" spans="1:10" customHeight="1" ht="15">
-      <c r="A77" s="2"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="33"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+    </row>
+    <row r="77" spans="1:10" customHeight="1" ht="39">
+      <c r="A77" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
     </row>
     <row r="78" spans="1:10" customHeight="1" ht="15">
       <c r="A78" s="32"/>
-      <c r="B78" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C78" s="34"/>
-      <c r="D78" s="34"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
+      <c r="G78" s="33"/>
+      <c r="H78" s="33"/>
+      <c r="I78" s="33"/>
     </row>
     <row r="79" spans="1:10" customHeight="1" ht="15">
       <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="36" t="s">
-        <v>115</v>
-      </c>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="33"/>
     </row>
     <row r="80" spans="1:10" customHeight="1" ht="15">
-      <c r="A80" s="2"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
+      <c r="G80" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="H80" s="35"/>
+      <c r="I80" s="35"/>
     </row>
     <row r="81" spans="1:10" customHeight="1" ht="15">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
+      <c r="D81" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -2313,68 +2345,90 @@
     </row>
     <row r="82" spans="1:10" customHeight="1" ht="15">
       <c r="A82" s="2"/>
-      <c r="B82" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
-      <c r="G82" s="34" t="str">
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+    </row>
+    <row r="83" spans="1:10" customHeight="1" ht="15">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:10" customHeight="1" ht="15">
+      <c r="A84" s="2"/>
+      <c r="B84" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C84" s="34"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="34" t="str">
         <f>C10</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="H82" s="34"/>
-      <c r="I82" s="34"/>
-    </row>
-    <row r="83" spans="1:10" customHeight="1" ht="15">
-      <c r="A83" s="2"/>
-      <c r="B83" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="34" t="str">
+      <c r="H84" s="34"/>
+      <c r="I84" s="34"/>
+    </row>
+    <row r="85" spans="1:10" customHeight="1" ht="15">
+      <c r="A85" s="2"/>
+      <c r="B85" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C85" s="34"/>
+      <c r="D85" s="34"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Información Financiera</v>
       </c>
-      <c r="H83" s="34"/>
-      <c r="I83" s="34"/>
-    </row>
-    <row r="84" spans="1:10" customHeight="1" ht="15">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-    </row>
-    <row r="85" spans="1:10" customHeight="1" ht="15">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
+      <c r="H85" s="34"/>
+      <c r="I85" s="34"/>
     </row>
     <row r="86" spans="1:10" customHeight="1" ht="15">
-      <c r="A86" s="32"/>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+    </row>
+    <row r="87" spans="1:10" customHeight="1" ht="15">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" spans="1:10" customHeight="1" ht="15">
+      <c r="A88" s="32"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -2393,23 +2447,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="H67:I67"/>
     <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A74:I74"/>
     <mergeCell ref="A75:I75"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="G85:I85"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -2548,7 +2602,13 @@
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="F64:G64"/>
     <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H19:I64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H19:I66"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>14/07/2025</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>Sala de control</t>
+    <t>re</t>
   </si>
   <si>
     <t>Región:</t>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>Base Operativa</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -946,7 +943,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -955,7 +952,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1004,24 +1001,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1032,17 +1029,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1055,17 +1052,17 @@
         <v>2</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="53" t="s">
         <v>26</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>27</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
@@ -1078,7 +1075,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="35"/>
@@ -1113,7 +1110,7 @@
     <row r="22" spans="1:11" customHeight="1" ht="15.75">
       <c r="A22" s="19"/>
       <c r="B22" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
@@ -1139,7 +1136,7 @@
     <row r="24" spans="1:11" customHeight="1" ht="15.75">
       <c r="A24" s="20"/>
       <c r="B24" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1153,7 +1150,7 @@
     <row r="25" spans="1:11" customHeight="1" ht="15">
       <c r="A25" s="20"/>
       <c r="B25" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1167,7 +1164,7 @@
     <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
       <c r="B26" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1181,7 +1178,7 @@
     <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1195,7 +1192,7 @@
     <row r="28" spans="1:11" customHeight="1" ht="15">
       <c r="A28" s="20"/>
       <c r="B28" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1221,7 +1218,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="27.75">
       <c r="A30" s="17"/>
       <c r="B30" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1253,12 +1250,12 @@
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="H33" s="34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
@@ -1275,7 +1272,7 @@
     <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
       <c r="C37" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -1288,12 +1285,12 @@
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
       <c r="C38" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
       <c r="H38" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>15/07/2025</t>
+    <t>16/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>re</t>
+    <t>rt</t>
   </si>
   <si>
     <t>Región:</t>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Ubicación:</t>
+  </si>
+  <si>
+    <t>rtr</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -943,7 +946,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -952,7 +955,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1001,24 +1004,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1029,17 +1032,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1052,17 +1055,17 @@
         <v>2</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
@@ -1075,7 +1078,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="35"/>
@@ -1110,7 +1113,7 @@
     <row r="22" spans="1:11" customHeight="1" ht="15.75">
       <c r="A22" s="19"/>
       <c r="B22" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
@@ -1136,7 +1139,7 @@
     <row r="24" spans="1:11" customHeight="1" ht="15.75">
       <c r="A24" s="20"/>
       <c r="B24" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -1150,7 +1153,7 @@
     <row r="25" spans="1:11" customHeight="1" ht="15">
       <c r="A25" s="20"/>
       <c r="B25" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -1164,7 +1167,7 @@
     <row r="26" spans="1:11" customHeight="1" ht="15">
       <c r="A26" s="20"/>
       <c r="B26" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
@@ -1178,7 +1181,7 @@
     <row r="27" spans="1:11" customHeight="1" ht="15">
       <c r="A27" s="20"/>
       <c r="B27" s="27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -1192,7 +1195,7 @@
     <row r="28" spans="1:11" customHeight="1" ht="15">
       <c r="A28" s="20"/>
       <c r="B28" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -1218,7 +1221,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="27.75">
       <c r="A30" s="17"/>
       <c r="B30" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1250,12 +1253,12 @@
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="H33" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
@@ -1272,7 +1275,7 @@
     <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="37" spans="1:11" customHeight="1" ht="15.75">
       <c r="C37" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -1285,12 +1288,12 @@
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
       <c r="C38" s="25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
       <c r="H38" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>16/07/2025</t>
+    <t>04/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>rt</t>
+    <t>d</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,9 +59,6 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>rtr</t>
-  </si>
-  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -83,25 +80,214 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Teléfono Celular</t>
-  </si>
-  <si>
-    <t>Poly</t>
-  </si>
-  <si>
-    <t>VVX 250</t>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Docking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>Linea: NA</t>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP Compaq Pro 6300</t>
+  </si>
+  <si>
+    <t>MXL31500FJ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00078</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>20-07-10112</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>JB6P283</t>
+  </si>
+  <si>
+    <t>KB3322Wt</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WW-A00</t>
+  </si>
+  <si>
+    <t>WM118t</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WW-A00</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FWT</t>
+  </si>
+  <si>
+    <t>BENQ</t>
+  </si>
+  <si>
+    <t>GW2780-T</t>
+  </si>
+  <si>
+    <t>ETK1N0041701Q</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WV-A00</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WV-A00</t>
+  </si>
+  <si>
+    <t>24-07-57974</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>JSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00086</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-00CU</t>
+  </si>
+  <si>
+    <t>827P283</t>
+  </si>
+  <si>
+    <t>22-04-05212</t>
+  </si>
+  <si>
+    <t>4TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00076</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>Lg</t>
+  </si>
+  <si>
+    <t>43UQ8008PSB</t>
+  </si>
+  <si>
+    <t>302MXAY5P136</t>
+  </si>
+  <si>
+    <t>1TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00117</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -410,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -528,9 +714,6 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,7 +990,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -946,7 +1129,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -955,7 +1138,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1004,24 +1187,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1032,17 +1215,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1051,265 +1234,1112 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>27</v>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
+        <v>25</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>25</v>
-      </c>
+      <c r="G18" s="53"/>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A19" s="18"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="54" t="s">
+    <row r="19" spans="1:11">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="31"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="18"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="19"/>
-      <c r="B22" s="33" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="9">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="20"/>
-      <c r="B24" s="27" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>3</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
+      <c r="D21" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="27" t="s">
+      <c r="D22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="12">
-      <c r="A29" s="21"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A30" s="17"/>
-      <c r="B30" s="29" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="25" t="s">
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="H33" s="34" t="s">
+      <c r="D23" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-    </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="25" t="s">
+      <c r="E23" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="H37" s="25" t="str">
+      <c r="F23" s="53"/>
+      <c r="G23" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53">
+        <v>6</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>7</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="53">
+        <v>1929</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53">
+        <v>730320922522</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>8</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>9</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53">
+        <v>10</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53">
+        <v>11</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53">
+        <v>12</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53">
+        <v>13</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
+        <v>14</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53">
+        <v>15</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
+        <v>16</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="52"/>
+      <c r="B36" s="53">
+        <v>17</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="52"/>
+      <c r="B37" s="53">
+        <v>18</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="52"/>
+      <c r="B38" s="53">
+        <v>19</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="52"/>
+      <c r="B39" s="53">
+        <v>20</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53">
+        <v>21</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="52"/>
+      <c r="B41" s="53">
+        <v>22</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53">
+        <v>23</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="52"/>
+      <c r="B43" s="53">
+        <v>24</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="52"/>
+      <c r="B45" s="53">
+        <v>25</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53">
+        <v>26</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="52"/>
+      <c r="B47" s="53">
+        <v>27</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53">
+        <v>28</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="52"/>
+      <c r="B49" s="53">
+        <v>29</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="52"/>
+      <c r="B50" s="53">
+        <v>30</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="52"/>
+      <c r="B51" s="53">
+        <v>31</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="52"/>
+      <c r="B52" s="53">
+        <v>32</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="52"/>
+      <c r="B54" s="53">
+        <v>33</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="52"/>
+      <c r="B55" s="53">
+        <v>34</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="52"/>
+      <c r="B56" s="53">
+        <v>35</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="52"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A58" s="18"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="31"/>
+    </row>
+    <row r="59" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A59" s="18"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="31"/>
+    </row>
+    <row r="60" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A61" s="19"/>
+      <c r="B61" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+    </row>
+    <row r="62" spans="1:11" customHeight="1" ht="9">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A63" s="20"/>
+      <c r="B63" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" customHeight="1" ht="15">
+      <c r="A64" s="20"/>
+      <c r="B64" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" customHeight="1" ht="15">
+      <c r="A65" s="20"/>
+      <c r="B65" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" customHeight="1" ht="15">
+      <c r="A66" s="20"/>
+      <c r="B66" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" customHeight="1" ht="15">
+      <c r="A67" s="20"/>
+      <c r="B67" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+    </row>
+    <row r="68" spans="1:11" customHeight="1" ht="12">
+      <c r="A68" s="21"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+    </row>
+    <row r="69" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A69" s="17"/>
+      <c r="B69" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+    </row>
+    <row r="70" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="H72" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+    </row>
+    <row r="73" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C76" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="H76" s="25" t="str">
         <f>C8</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="H38" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C77" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="H77" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1324,33 +2354,150 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I17:J57"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -41,7 +41,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>04/08/2025</t>
+    <t>05/08/2025</t>
   </si>
   <si>
     <t>Área:</t>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>19/08/2025</t>
+    <t>10/09/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>dsa</t>
+    <t>x</t>
   </si>
   <si>
     <t>Región:</t>
@@ -80,22 +80,214 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Teléfono celular</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Docking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>dasdghjdhkjadjfsbmhdkjlañhvskdljolhkjsladjvkbhdsambnsdlnms, m</t>
-  </si>
-  <si>
-    <t>Linea: NA</t>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP Compaq Pro 6300</t>
+  </si>
+  <si>
+    <t>MXL31500FJ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00078</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>20-07-10112</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>JB6P283</t>
+  </si>
+  <si>
+    <t>KB3322Wt</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WW-A00</t>
+  </si>
+  <si>
+    <t>WM118t</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WW-A00</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FWT</t>
+  </si>
+  <si>
+    <t>BENQ</t>
+  </si>
+  <si>
+    <t>GW2780-T</t>
+  </si>
+  <si>
+    <t>ETK1N0041701Q</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WV-A00</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WV-A00</t>
+  </si>
+  <si>
+    <t>24-07-57974</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>JSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00086</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-00CU</t>
+  </si>
+  <si>
+    <t>827P283</t>
+  </si>
+  <si>
+    <t>22-04-05212</t>
+  </si>
+  <si>
+    <t>4TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00076</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>Lg</t>
+  </si>
+  <si>
+    <t>43UQ8008PSB</t>
+  </si>
+  <si>
+    <t>302MXAY5P136</t>
+  </si>
+  <si>
+    <t>1TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00117</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -404,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -522,9 +714,6 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,7 +990,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1039,250 +1228,1118 @@
         <v>24</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53" t="s">
-        <v>25</v>
-      </c>
+      <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="54" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="31"/>
-    </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A19" s="18"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="19"/>
-      <c r="B21" s="33" t="s">
+      <c r="D19" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="9">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="20"/>
-      <c r="B23" s="27" t="s">
+      <c r="F19" s="53"/>
+      <c r="G19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15">
-      <c r="A24" s="20"/>
-      <c r="B24" s="27" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>3</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
+      <c r="D21" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="12">
-      <c r="A28" s="21"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A29" s="17"/>
-      <c r="B29" s="29" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="25" t="s">
+      <c r="D22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="H32" s="34" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C36" s="25" t="s">
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="H36" s="25" t="str">
+      <c r="D23" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53">
+        <v>6</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>7</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="53">
+        <v>1929</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53">
+        <v>730320922522</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>8</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>9</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53">
+        <v>10</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53">
+        <v>11</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53">
+        <v>12</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53">
+        <v>13</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
+        <v>14</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53">
+        <v>15</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
+        <v>16</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="52"/>
+      <c r="B36" s="53">
+        <v>17</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="52"/>
+      <c r="B37" s="53">
+        <v>18</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="52"/>
+      <c r="B38" s="53">
+        <v>19</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="52"/>
+      <c r="B39" s="53">
+        <v>20</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53">
+        <v>21</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="52"/>
+      <c r="B41" s="53">
+        <v>22</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53">
+        <v>23</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="52"/>
+      <c r="B43" s="53">
+        <v>24</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="52"/>
+      <c r="B45" s="53">
+        <v>25</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53">
+        <v>26</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="52"/>
+      <c r="B47" s="53">
+        <v>27</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53">
+        <v>28</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="52"/>
+      <c r="B49" s="53">
+        <v>29</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="52"/>
+      <c r="B50" s="53">
+        <v>30</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="52"/>
+      <c r="B51" s="53">
+        <v>31</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="52"/>
+      <c r="B52" s="53">
+        <v>32</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="52"/>
+      <c r="B54" s="53">
+        <v>33</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="52"/>
+      <c r="B55" s="53">
+        <v>34</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="52"/>
+      <c r="B56" s="53">
+        <v>35</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="52"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A58" s="18"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="31"/>
+    </row>
+    <row r="59" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A59" s="18"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="31"/>
+    </row>
+    <row r="60" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A61" s="19"/>
+      <c r="B61" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+    </row>
+    <row r="62" spans="1:11" customHeight="1" ht="9">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A63" s="20"/>
+      <c r="B63" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" customHeight="1" ht="15">
+      <c r="A64" s="20"/>
+      <c r="B64" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" customHeight="1" ht="15">
+      <c r="A65" s="20"/>
+      <c r="B65" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" customHeight="1" ht="15">
+      <c r="A66" s="20"/>
+      <c r="B66" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" customHeight="1" ht="15">
+      <c r="A67" s="20"/>
+      <c r="B67" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+    </row>
+    <row r="68" spans="1:11" customHeight="1" ht="12">
+      <c r="A68" s="21"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+    </row>
+    <row r="69" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A69" s="17"/>
+      <c r="B69" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+    </row>
+    <row r="70" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="H72" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+    </row>
+    <row r="73" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C76" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="H76" s="25" t="str">
         <f>C8</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="H37" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C77" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="H77" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1297,29 +2354,150 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I17:J57"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="105">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/09/2025</t>
+    <t>02/10/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>fgh</t>
+    <t>Base Operativa</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>fdgh</t>
+    <t>ti</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>Prueba</t>
   </si>
   <si>
     <t>DVZ-VH-TI-00050</t>
@@ -1231,7 +1234,9 @@
         <v>25</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
+      <c r="I17" s="53" t="s">
+        <v>26</v>
+      </c>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
@@ -1241,7 +1246,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1256,17 +1261,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1279,7 +1284,7 @@
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="E20" s="51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
@@ -1294,17 +1299,17 @@
         <v>3</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1317,17 +1322,17 @@
         <v>4</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1340,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53">
@@ -1363,13 +1368,13 @@
         <v>6</v>
       </c>
       <c r="C24" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>40</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>39</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53">
@@ -1386,10 +1391,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E25" s="53">
         <v>1929</v>
@@ -1409,17 +1414,17 @@
         <v>8</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1432,17 +1437,17 @@
         <v>9</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F27" s="53"/>
       <c r="G27" s="53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
@@ -1455,17 +1460,17 @@
         <v>10</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F28" s="53"/>
       <c r="G28" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H28" s="53"/>
       <c r="I28" s="53"/>
@@ -1478,17 +1483,17 @@
         <v>11</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E29" s="53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29" s="53"/>
       <c r="G29" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
@@ -1501,7 +1506,7 @@
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
       <c r="E30" s="51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F30" s="53"/>
       <c r="G30" s="53"/>
@@ -1516,13 +1521,13 @@
         <v>12</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31" s="53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F31" s="53"/>
       <c r="G31" s="53">
@@ -1539,13 +1544,13 @@
         <v>13</v>
       </c>
       <c r="C32" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="53" t="s">
         <v>40</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>39</v>
       </c>
       <c r="F32" s="53"/>
       <c r="G32" s="53">
@@ -1562,17 +1567,17 @@
         <v>14</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" s="53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F33" s="53"/>
       <c r="G33" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H33" s="53"/>
       <c r="I33" s="53"/>
@@ -1585,17 +1590,17 @@
         <v>15</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" s="53"/>
       <c r="G34" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H34" s="53"/>
       <c r="I34" s="53"/>
@@ -1608,17 +1613,17 @@
         <v>16</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D35" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F35" s="53"/>
       <c r="G35" s="53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H35" s="53"/>
       <c r="I35" s="53"/>
@@ -1631,17 +1636,17 @@
         <v>17</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D36" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="53"/>
       <c r="G36" s="53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H36" s="53"/>
       <c r="I36" s="53"/>
@@ -1654,17 +1659,17 @@
         <v>18</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D37" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F37" s="53"/>
       <c r="G37" s="53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
@@ -1677,17 +1682,17 @@
         <v>19</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E38" s="53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" s="53"/>
       <c r="G38" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H38" s="53"/>
       <c r="I38" s="53"/>
@@ -1700,17 +1705,17 @@
         <v>20</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E39" s="53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F39" s="53"/>
       <c r="G39" s="53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
@@ -1723,17 +1728,17 @@
         <v>21</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="53"/>
       <c r="G40" s="53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
@@ -1746,17 +1751,17 @@
         <v>22</v>
       </c>
       <c r="C41" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D41" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F41" s="53"/>
       <c r="G41" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
@@ -1769,17 +1774,17 @@
         <v>23</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E42" s="53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F42" s="53"/>
       <c r="G42" s="53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H42" s="53"/>
       <c r="I42" s="53"/>
@@ -1792,17 +1797,17 @@
         <v>24</v>
       </c>
       <c r="C43" s="53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H43" s="53"/>
       <c r="I43" s="53"/>
@@ -1815,7 +1820,7 @@
       <c r="C44" s="53"/>
       <c r="D44" s="53"/>
       <c r="E44" s="51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F44" s="53"/>
       <c r="G44" s="53"/>
@@ -1830,17 +1835,17 @@
         <v>25</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D45" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F45" s="53"/>
       <c r="G45" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H45" s="53"/>
       <c r="I45" s="53"/>
@@ -1853,17 +1858,17 @@
         <v>26</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D46" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F46" s="53"/>
       <c r="G46" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" s="53"/>
       <c r="I46" s="53"/>
@@ -1876,17 +1881,17 @@
         <v>27</v>
       </c>
       <c r="C47" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D47" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F47" s="53"/>
       <c r="G47" s="53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H47" s="53"/>
       <c r="I47" s="53"/>
@@ -1899,17 +1904,17 @@
         <v>28</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F48" s="53"/>
       <c r="G48" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H48" s="53"/>
       <c r="I48" s="53"/>
@@ -1922,13 +1927,13 @@
         <v>29</v>
       </c>
       <c r="C49" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="53" t="s">
         <v>40</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>39</v>
       </c>
       <c r="F49" s="53"/>
       <c r="G49" s="53">
@@ -1945,13 +1950,13 @@
         <v>30</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D50" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E50" s="53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F50" s="53"/>
       <c r="G50" s="53">
@@ -1968,17 +1973,17 @@
         <v>31</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E51" s="53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F51" s="53"/>
       <c r="G51" s="53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H51" s="53"/>
       <c r="I51" s="53"/>
@@ -1991,17 +1996,17 @@
         <v>32</v>
       </c>
       <c r="C52" s="53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E52" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F52" s="53"/>
       <c r="G52" s="53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -2014,7 +2019,7 @@
       <c r="C53" s="53"/>
       <c r="D53" s="53"/>
       <c r="E53" s="51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F53" s="53"/>
       <c r="G53" s="53"/>
@@ -2029,17 +2034,17 @@
         <v>33</v>
       </c>
       <c r="C54" s="53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D54" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E54" s="53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F54" s="53"/>
       <c r="G54" s="53" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="53"/>
@@ -2052,17 +2057,17 @@
         <v>34</v>
       </c>
       <c r="C55" s="53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55" s="53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F55" s="53"/>
       <c r="G55" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H55" s="53"/>
       <c r="I55" s="53"/>
@@ -2075,17 +2080,17 @@
         <v>35</v>
       </c>
       <c r="C56" s="53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D56" s="53" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F56" s="53"/>
       <c r="G56" s="53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H56" s="53"/>
       <c r="I56" s="53"/>
@@ -2098,7 +2103,7 @@
       <c r="C57" s="53"/>
       <c r="D57" s="53"/>
       <c r="E57" s="51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F57" s="53"/>
       <c r="G57" s="53"/>
@@ -2146,7 +2151,7 @@
     <row r="61" spans="1:11" customHeight="1" ht="15.75">
       <c r="A61" s="19"/>
       <c r="B61" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C61" s="26"/>
       <c r="D61" s="26"/>
@@ -2172,7 +2177,7 @@
     <row r="63" spans="1:11" customHeight="1" ht="15.75">
       <c r="A63" s="20"/>
       <c r="B63" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C63" s="26"/>
       <c r="D63" s="26"/>
@@ -2186,7 +2191,7 @@
     <row r="64" spans="1:11" customHeight="1" ht="15">
       <c r="A64" s="20"/>
       <c r="B64" s="27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C64" s="26"/>
       <c r="D64" s="26"/>
@@ -2200,7 +2205,7 @@
     <row r="65" spans="1:11" customHeight="1" ht="15">
       <c r="A65" s="20"/>
       <c r="B65" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C65" s="26"/>
       <c r="D65" s="26"/>
@@ -2214,7 +2219,7 @@
     <row r="66" spans="1:11" customHeight="1" ht="15">
       <c r="A66" s="20"/>
       <c r="B66" s="27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C66" s="26"/>
       <c r="D66" s="26"/>
@@ -2228,7 +2233,7 @@
     <row r="67" spans="1:11" customHeight="1" ht="15">
       <c r="A67" s="20"/>
       <c r="B67" s="27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C67" s="26"/>
       <c r="D67" s="26"/>
@@ -2254,7 +2259,7 @@
     <row r="69" spans="1:11" customHeight="1" ht="27.75">
       <c r="A69" s="17"/>
       <c r="B69" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C69" s="26"/>
       <c r="D69" s="26"/>
@@ -2286,12 +2291,12 @@
       <c r="A72" s="22"/>
       <c r="B72" s="22"/>
       <c r="C72" s="25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="26"/>
       <c r="H72" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I72" s="26"/>
       <c r="J72" s="26"/>
@@ -2308,7 +2313,7 @@
     <row r="75" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="76" spans="1:11" customHeight="1" ht="15.75">
       <c r="C76" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="26"/>
@@ -2321,12 +2326,12 @@
     </row>
     <row r="77" spans="1:11" customHeight="1" ht="15.75">
       <c r="C77" s="25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="26"/>
       <c r="H77" s="25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I77" s="26"/>
       <c r="J77" s="26"/>

--- a/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
+++ b/database/controller_excel/Resguardo_Cristell_Hernandez_Contreras.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="105">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>03/12/2025</t>
+    <t>20/01/2026</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>ERYTU</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
+    <t>QWERT</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -83,22 +83,217 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Teléfono celular</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>7BV9FG3</t>
+  </si>
+  <si>
+    <t>ASFDGHKUIJLOÑ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00050</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Optiplex 3050</t>
+  </si>
+  <si>
+    <t>9NK8CM2</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00079</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>3W9J0C3</t>
+  </si>
+  <si>
+    <t>Cargador de Docking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BPO-A04</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>ACTECK</t>
+  </si>
+  <si>
+    <t>MK450</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>E2724HS</t>
+  </si>
+  <si>
+    <t>6W69G04</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216R</t>
+  </si>
+  <si>
+    <t>23-08-29697</t>
+  </si>
+  <si>
+    <t>Mochila</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Prueba</t>
-  </si>
-  <si>
-    <t>Linea: NA</t>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP Compaq Pro 6300</t>
+  </si>
+  <si>
+    <t>MXL31500FJ</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00078</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>20-07-10112</t>
+  </si>
+  <si>
+    <t>E2720HS</t>
+  </si>
+  <si>
+    <t>JB6P283</t>
+  </si>
+  <si>
+    <t>KB3322Wt</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WW-A00</t>
+  </si>
+  <si>
+    <t>WM118t</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WW-A00</t>
+  </si>
+  <si>
+    <t>EliteDisplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FWT</t>
+  </si>
+  <si>
+    <t>BENQ</t>
+  </si>
+  <si>
+    <t>GW2780-T</t>
+  </si>
+  <si>
+    <t>ETK1N0041701Q</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-M6WV-A00</t>
+  </si>
+  <si>
+    <t>CN-0255KM-LO300-217-K6WV-A00</t>
+  </si>
+  <si>
+    <t>24-07-57974</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>JSYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00086</t>
+  </si>
+  <si>
+    <t>KB216T</t>
+  </si>
+  <si>
+    <t>CN-0F2JV2-LO300-0CE-00LT-A04</t>
+  </si>
+  <si>
+    <t>MS116T1</t>
+  </si>
+  <si>
+    <t>CN-065K5F-LO300-150-00CU</t>
+  </si>
+  <si>
+    <t>827P283</t>
+  </si>
+  <si>
+    <t>22-04-05212</t>
+  </si>
+  <si>
+    <t>4TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00076</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18L-2MZ1-A02</t>
+  </si>
+  <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>Lg</t>
+  </si>
+  <si>
+    <t>43UQ8008PSB</t>
+  </si>
+  <si>
+    <t>302MXAY5P136</t>
+  </si>
+  <si>
+    <t>1TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00117</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -128,7 +323,7 @@
     <t>ACEPTA Y RECIBE:</t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
+    <t>Alejandro Cancino Argüello</t>
   </si>
   <si>
     <t>Coordinador de TI</t>
@@ -407,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -525,9 +720,6 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -804,7 +996,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1048,244 +1240,1114 @@
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A18" s="18"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="54" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="31"/>
-    </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A19" s="18"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="19"/>
-      <c r="B21" s="33" t="s">
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="9">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="20"/>
-      <c r="B23" s="27" t="s">
+      <c r="D19" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15">
-      <c r="A24" s="20"/>
-      <c r="B24" s="27" t="s">
+      <c r="F19" s="53"/>
+      <c r="G19" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="27" t="s">
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>3</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
+      <c r="D21" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="12">
-      <c r="A28" s="21"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A29" s="17"/>
-      <c r="B29" s="29" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="25" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="H32" s="34" t="s">
+      <c r="D22" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C36" s="25" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="H36" s="25" t="str">
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53">
+        <v>6</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53">
+        <v>368631741364</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>7</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="53">
+        <v>1929</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53">
+        <v>730320922522</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>8</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>9</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53">
+        <v>10</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53">
+        <v>11</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53">
+        <v>12</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53">
+        <v>13</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53">
+        <v>368631740944</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
+        <v>14</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53">
+        <v>15</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
+        <v>16</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="52"/>
+      <c r="B36" s="53">
+        <v>17</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="52"/>
+      <c r="B37" s="53">
+        <v>18</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="52"/>
+      <c r="B38" s="53">
+        <v>19</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="52"/>
+      <c r="B39" s="53">
+        <v>20</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="52"/>
+      <c r="B40" s="53">
+        <v>21</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="52"/>
+      <c r="B41" s="53">
+        <v>22</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53">
+        <v>23</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="52"/>
+      <c r="B43" s="53">
+        <v>24</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="52"/>
+      <c r="B45" s="53">
+        <v>25</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="52"/>
+      <c r="B46" s="53">
+        <v>26</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="52"/>
+      <c r="B47" s="53">
+        <v>27</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53">
+        <v>28</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="52"/>
+      <c r="B49" s="53">
+        <v>29</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="52"/>
+      <c r="B50" s="53">
+        <v>30</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53">
+        <v>368631741367</v>
+      </c>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="52"/>
+      <c r="B51" s="53">
+        <v>31</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="52"/>
+      <c r="B52" s="53">
+        <v>32</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="52"/>
+      <c r="B54" s="53">
+        <v>33</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="52"/>
+      <c r="B55" s="53">
+        <v>34</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="52"/>
+      <c r="B56" s="53">
+        <v>35</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="52"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A58" s="18"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="31"/>
+    </row>
+    <row r="59" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A59" s="18"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="31"/>
+    </row>
+    <row r="60" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A61" s="19"/>
+      <c r="B61" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+    </row>
+    <row r="62" spans="1:11" customHeight="1" ht="9">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A63" s="20"/>
+      <c r="B63" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" customHeight="1" ht="15">
+      <c r="A64" s="20"/>
+      <c r="B64" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+    </row>
+    <row r="65" spans="1:11" customHeight="1" ht="15">
+      <c r="A65" s="20"/>
+      <c r="B65" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+    </row>
+    <row r="66" spans="1:11" customHeight="1" ht="15">
+      <c r="A66" s="20"/>
+      <c r="B66" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+    </row>
+    <row r="67" spans="1:11" customHeight="1" ht="15">
+      <c r="A67" s="20"/>
+      <c r="B67" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+    </row>
+    <row r="68" spans="1:11" customHeight="1" ht="12">
+      <c r="A68" s="21"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+    </row>
+    <row r="69" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A69" s="17"/>
+      <c r="B69" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+    </row>
+    <row r="70" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="H72" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+    </row>
+    <row r="73" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C76" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="H76" s="25" t="str">
         <f>C8</f>
         <v>Cristell Hernandez Contreras</v>
       </c>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="H37" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+    </row>
+    <row r="77" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C77" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="H77" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+    </row>
+    <row r="78" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+    </row>
+    <row r="79" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1300,29 +2362,150 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="B64:J64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I17:J57"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
